--- a/data/raw/GLNPO 2024 Spring/Ontario/D100/ON 12 D100 Spring 2024 24GO00I93 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Ontario/D100/ON 12 D100 Spring 2024 24GO00I93 Zoop.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gl Lab User\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Ontario\D100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69DCC855-B91E-437E-BE98-D20024FB728B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB15B164-67EE-4635-9296-76075D4C6044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{F79D184D-9308-4C2F-9BD8-2D0762B00D0D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F79D184D-9308-4C2F-9BD8-2D0762B00D0D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$Y$241</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$241</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId2"/>
+    <pivotCache cacheId="15" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -140,9 +140,6 @@
     <t>CYCCOPE</t>
   </si>
   <si>
-    <t>CYCIMM</t>
-  </si>
-  <si>
     <t>IMM</t>
   </si>
   <si>
@@ -165,9 +162,6 @@
   </si>
   <si>
     <t>DIACOPE</t>
-  </si>
-  <si>
-    <t>CALIMM</t>
   </si>
   <si>
     <t>Leptodiaptomus minutus</t>
@@ -285,6 +279,12 @@
   </si>
   <si>
     <t>No animals present in D split</t>
+  </si>
+  <si>
+    <t>CALIMM</t>
+  </si>
+  <si>
+    <t>CYCIMM</t>
   </si>
 </sst>
 </file>
@@ -5281,7 +5281,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C5DCCCEA-4A8C-4A62-AC78-47C56870DB35}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C5DCCCEA-4A8C-4A62-AC78-47C56870DB35}" name="PivotTable1" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="T3:Y17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField showAll="0"/>
@@ -5723,21 +5723,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E093411B-5FC0-41F2-9B42-F2A8D6145550}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:Y241"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.6640625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="9" customWidth="1"/>
-    <col min="20" max="20" width="16.7109375" customWidth="1"/>
-    <col min="21" max="21" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.42578125" customWidth="1"/>
-    <col min="23" max="23" width="4.85546875" customWidth="1"/>
-    <col min="24" max="24" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.6640625" customWidth="1"/>
+    <col min="21" max="21" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.44140625" customWidth="1"/>
+    <col min="23" max="23" width="4.88671875" customWidth="1"/>
+    <col min="24" max="24" width="2.88671875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5793,7 +5794,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -5846,7 +5847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -5899,13 +5900,13 @@
         <v>1</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="U3" s="6" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -5943,40 +5944,40 @@
         <v>31</v>
       </c>
       <c r="M4" t="s">
+        <v>80</v>
+      </c>
+      <c r="N4" t="s">
         <v>32</v>
-      </c>
-      <c r="N4" t="s">
-        <v>33</v>
       </c>
       <c r="O4">
         <v>0.88900000000000001</v>
       </c>
       <c r="P4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q4">
         <v>1</v>
       </c>
       <c r="T4" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="U4" t="s">
         <v>21</v>
       </c>
       <c r="V4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="W4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="X4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Y4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -6029,7 +6030,7 @@
         <v>1</v>
       </c>
       <c r="T5" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="U5">
         <v>22</v>
@@ -6041,7 +6042,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -6079,16 +6080,16 @@
         <v>31</v>
       </c>
       <c r="M6" t="s">
+        <v>80</v>
+      </c>
+      <c r="N6" t="s">
         <v>32</v>
-      </c>
-      <c r="N6" t="s">
-        <v>33</v>
       </c>
       <c r="O6">
         <v>0.83699999999999997</v>
       </c>
       <c r="P6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q6">
         <v>1</v>
@@ -6106,7 +6107,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -6138,28 +6139,28 @@
         <v>24</v>
       </c>
       <c r="K7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" t="s">
         <v>35</v>
       </c>
-      <c r="L7" t="s">
+      <c r="M7" t="s">
         <v>36</v>
       </c>
-      <c r="M7" t="s">
+      <c r="N7" t="s">
         <v>37</v>
-      </c>
-      <c r="N7" t="s">
-        <v>38</v>
       </c>
       <c r="O7">
         <v>0.53100000000000003</v>
       </c>
       <c r="P7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q7">
         <v>1</v>
       </c>
       <c r="T7" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="U7">
         <v>6</v>
@@ -6174,7 +6175,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -6227,7 +6228,7 @@
         <v>1</v>
       </c>
       <c r="T8" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="U8">
         <v>6</v>
@@ -6242,7 +6243,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -6274,22 +6275,22 @@
         <v>24</v>
       </c>
       <c r="K9" t="s">
+        <v>38</v>
+      </c>
+      <c r="L9" t="s">
         <v>39</v>
       </c>
-      <c r="L9" t="s">
-        <v>40</v>
-      </c>
       <c r="M9" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O9">
         <v>0.54</v>
       </c>
       <c r="P9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q9">
         <v>1</v>
@@ -6307,7 +6308,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -6339,28 +6340,28 @@
         <v>24</v>
       </c>
       <c r="K10" t="s">
+        <v>38</v>
+      </c>
+      <c r="L10" t="s">
         <v>39</v>
       </c>
-      <c r="L10" t="s">
-        <v>40</v>
-      </c>
       <c r="M10" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O10">
         <v>0.57299999999999995</v>
       </c>
       <c r="P10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q10">
         <v>1</v>
       </c>
       <c r="T10" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="U10">
         <v>108</v>
@@ -6372,7 +6373,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -6425,7 +6426,7 @@
         <v>1</v>
       </c>
       <c r="T11" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="U11">
         <v>0</v>
@@ -6440,7 +6441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -6472,28 +6473,28 @@
         <v>24</v>
       </c>
       <c r="K12" t="s">
+        <v>38</v>
+      </c>
+      <c r="L12" t="s">
         <v>39</v>
       </c>
-      <c r="L12" t="s">
-        <v>40</v>
-      </c>
       <c r="M12" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O12">
         <v>0.60299999999999998</v>
       </c>
       <c r="P12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q12">
         <v>1</v>
       </c>
       <c r="T12" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="U12">
         <v>19</v>
@@ -6508,7 +6509,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -6540,28 +6541,28 @@
         <v>24</v>
       </c>
       <c r="K13" t="s">
+        <v>38</v>
+      </c>
+      <c r="L13" t="s">
         <v>39</v>
       </c>
-      <c r="L13" t="s">
-        <v>40</v>
-      </c>
       <c r="M13" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O13">
         <v>0.53700000000000003</v>
       </c>
       <c r="P13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q13">
         <v>1</v>
       </c>
       <c r="T13" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="U13">
         <v>3</v>
@@ -6576,7 +6577,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -6608,28 +6609,28 @@
         <v>24</v>
       </c>
       <c r="K14" t="s">
+        <v>38</v>
+      </c>
+      <c r="L14" t="s">
         <v>39</v>
       </c>
-      <c r="L14" t="s">
-        <v>40</v>
-      </c>
       <c r="M14" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O14">
         <v>0.75</v>
       </c>
       <c r="P14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q14">
         <v>1</v>
       </c>
       <c r="T14" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="U14">
         <v>7</v>
@@ -6644,7 +6645,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -6676,28 +6677,28 @@
         <v>24</v>
       </c>
       <c r="K15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L15" t="s">
         <v>39</v>
       </c>
-      <c r="L15" t="s">
-        <v>40</v>
-      </c>
       <c r="M15" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O15">
         <v>0.88800000000000001</v>
       </c>
       <c r="P15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q15">
         <v>1</v>
       </c>
       <c r="T15" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="X15">
         <v>6</v>
@@ -6706,7 +6707,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -6738,28 +6739,28 @@
         <v>24</v>
       </c>
       <c r="K16" t="s">
+        <v>38</v>
+      </c>
+      <c r="L16" t="s">
         <v>39</v>
       </c>
-      <c r="L16" t="s">
-        <v>40</v>
-      </c>
       <c r="M16" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O16">
         <v>0.55200000000000005</v>
       </c>
       <c r="P16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q16">
         <v>1</v>
       </c>
       <c r="T16" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="U16">
         <v>5</v>
@@ -6774,7 +6775,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -6806,13 +6807,13 @@
         <v>24</v>
       </c>
       <c r="K17" t="s">
+        <v>40</v>
+      </c>
+      <c r="L17" t="s">
+        <v>41</v>
+      </c>
+      <c r="M17" t="s">
         <v>42</v>
-      </c>
-      <c r="L17" t="s">
-        <v>43</v>
-      </c>
-      <c r="M17" t="s">
-        <v>44</v>
       </c>
       <c r="N17" t="s">
         <v>28</v>
@@ -6821,13 +6822,13 @@
         <v>1.19</v>
       </c>
       <c r="P17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q17">
         <v>1</v>
       </c>
       <c r="T17" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="U17">
         <v>325</v>
@@ -6845,7 +6846,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -6883,22 +6884,22 @@
         <v>31</v>
       </c>
       <c r="M18" t="s">
+        <v>80</v>
+      </c>
+      <c r="N18" t="s">
         <v>32</v>
-      </c>
-      <c r="N18" t="s">
-        <v>33</v>
       </c>
       <c r="O18">
         <v>0.80900000000000005</v>
       </c>
       <c r="P18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q18">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -6936,31 +6937,31 @@
         <v>31</v>
       </c>
       <c r="M19" t="s">
+        <v>80</v>
+      </c>
+      <c r="N19" t="s">
         <v>32</v>
-      </c>
-      <c r="N19" t="s">
-        <v>33</v>
       </c>
       <c r="O19">
         <v>0.93</v>
       </c>
       <c r="P19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q19">
         <v>1</v>
       </c>
       <c r="T19" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="U19" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="V19" s="8">
         <v>1.004</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -7014,13 +7015,13 @@
       </c>
       <c r="T20" s="8"/>
       <c r="U20" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="V20" s="8">
         <v>1.0029999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -7058,31 +7059,31 @@
         <v>31</v>
       </c>
       <c r="M21" t="s">
+        <v>80</v>
+      </c>
+      <c r="N21" t="s">
         <v>32</v>
-      </c>
-      <c r="N21" t="s">
-        <v>33</v>
       </c>
       <c r="O21">
         <v>0.73799999999999999</v>
       </c>
       <c r="P21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q21">
         <v>1</v>
       </c>
       <c r="T21" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="U21" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="V21" s="8">
         <v>0.99</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -7120,29 +7121,29 @@
         <v>31</v>
       </c>
       <c r="M22" t="s">
+        <v>80</v>
+      </c>
+      <c r="N22" t="s">
         <v>32</v>
-      </c>
-      <c r="N22" t="s">
-        <v>33</v>
       </c>
       <c r="O22">
         <v>0.92600000000000005</v>
       </c>
       <c r="P22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q22">
         <v>1</v>
       </c>
       <c r="T22" s="8"/>
       <c r="U22" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="V22" s="8">
         <v>1.0009999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -7174,35 +7175,35 @@
         <v>24</v>
       </c>
       <c r="K23" t="s">
+        <v>38</v>
+      </c>
+      <c r="L23" t="s">
         <v>39</v>
       </c>
-      <c r="L23" t="s">
-        <v>40</v>
-      </c>
       <c r="M23" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O23">
         <v>0.53400000000000003</v>
       </c>
       <c r="P23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q23">
         <v>1</v>
       </c>
       <c r="T23" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="U23" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="V23" s="8"/>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -7255,14 +7256,14 @@
         <v>1</v>
       </c>
       <c r="T24" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="U24" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="V24" s="8"/>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -7315,13 +7316,13 @@
         <v>1</v>
       </c>
       <c r="T25" s="8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="U25" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -7359,22 +7360,22 @@
         <v>31</v>
       </c>
       <c r="M26" t="s">
+        <v>80</v>
+      </c>
+      <c r="N26" t="s">
         <v>32</v>
-      </c>
-      <c r="N26" t="s">
-        <v>33</v>
       </c>
       <c r="O26">
         <v>0.97699999999999998</v>
       </c>
       <c r="P26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q26">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -7427,7 +7428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -7459,28 +7460,28 @@
         <v>24</v>
       </c>
       <c r="K28" t="s">
+        <v>38</v>
+      </c>
+      <c r="L28" t="s">
         <v>39</v>
       </c>
-      <c r="L28" t="s">
-        <v>40</v>
-      </c>
       <c r="M28" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O28">
         <v>0.72699999999999998</v>
       </c>
       <c r="P28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q28">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -7533,7 +7534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -7571,22 +7572,22 @@
         <v>31</v>
       </c>
       <c r="M30" t="s">
+        <v>80</v>
+      </c>
+      <c r="N30" t="s">
         <v>32</v>
-      </c>
-      <c r="N30" t="s">
-        <v>33</v>
       </c>
       <c r="O30">
         <v>0.46800000000000003</v>
       </c>
       <c r="P30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q30">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -7639,7 +7640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -7671,28 +7672,28 @@
         <v>24</v>
       </c>
       <c r="K32" t="s">
+        <v>38</v>
+      </c>
+      <c r="L32" t="s">
         <v>39</v>
       </c>
-      <c r="L32" t="s">
-        <v>40</v>
-      </c>
       <c r="M32" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O32">
         <v>0.56399999999999995</v>
       </c>
       <c r="P32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q32">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -7724,13 +7725,13 @@
         <v>24</v>
       </c>
       <c r="K33" t="s">
+        <v>40</v>
+      </c>
+      <c r="L33" t="s">
+        <v>41</v>
+      </c>
+      <c r="M33" t="s">
         <v>42</v>
-      </c>
-      <c r="L33" t="s">
-        <v>43</v>
-      </c>
-      <c r="M33" t="s">
-        <v>44</v>
       </c>
       <c r="N33" t="s">
         <v>28</v>
@@ -7739,13 +7740,13 @@
         <v>1.0860000000000001</v>
       </c>
       <c r="P33" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q33">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -7792,13 +7793,13 @@
         <v>0.98399999999999999</v>
       </c>
       <c r="P34" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q34">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -7830,28 +7831,28 @@
         <v>24</v>
       </c>
       <c r="K35" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L35" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M35" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O35">
         <v>0.93500000000000005</v>
       </c>
       <c r="P35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q35">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -7883,28 +7884,28 @@
         <v>24</v>
       </c>
       <c r="K36" t="s">
+        <v>38</v>
+      </c>
+      <c r="L36" t="s">
         <v>39</v>
       </c>
-      <c r="L36" t="s">
-        <v>40</v>
-      </c>
       <c r="M36" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N36" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O36">
         <v>0.72699999999999998</v>
       </c>
       <c r="P36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q36">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -7936,28 +7937,28 @@
         <v>24</v>
       </c>
       <c r="K37" t="s">
+        <v>38</v>
+      </c>
+      <c r="L37" t="s">
         <v>39</v>
       </c>
-      <c r="L37" t="s">
-        <v>40</v>
-      </c>
       <c r="M37" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N37" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O37">
         <v>0.59799999999999998</v>
       </c>
       <c r="P37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q37">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -8010,7 +8011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -8042,13 +8043,13 @@
         <v>24</v>
       </c>
       <c r="K39" t="s">
+        <v>40</v>
+      </c>
+      <c r="L39" t="s">
+        <v>41</v>
+      </c>
+      <c r="M39" t="s">
         <v>42</v>
-      </c>
-      <c r="L39" t="s">
-        <v>43</v>
-      </c>
-      <c r="M39" t="s">
-        <v>44</v>
       </c>
       <c r="N39" t="s">
         <v>28</v>
@@ -8063,7 +8064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -8110,13 +8111,13 @@
         <v>1.208</v>
       </c>
       <c r="P40" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q40">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -8163,13 +8164,13 @@
         <v>0.95</v>
       </c>
       <c r="P41" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q41">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -8222,7 +8223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -8254,13 +8255,13 @@
         <v>24</v>
       </c>
       <c r="K43" t="s">
+        <v>40</v>
+      </c>
+      <c r="L43" t="s">
+        <v>41</v>
+      </c>
+      <c r="M43" t="s">
         <v>42</v>
-      </c>
-      <c r="L43" t="s">
-        <v>43</v>
-      </c>
-      <c r="M43" t="s">
-        <v>44</v>
       </c>
       <c r="N43" t="s">
         <v>28</v>
@@ -8269,13 +8270,13 @@
         <v>1.01</v>
       </c>
       <c r="P43" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q43">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -8328,7 +8329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -8360,28 +8361,28 @@
         <v>24</v>
       </c>
       <c r="K45" t="s">
+        <v>38</v>
+      </c>
+      <c r="L45" t="s">
         <v>39</v>
       </c>
-      <c r="L45" t="s">
-        <v>40</v>
-      </c>
       <c r="M45" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N45" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O45">
         <v>0.73799999999999999</v>
       </c>
       <c r="P45" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q45">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -8413,28 +8414,28 @@
         <v>24</v>
       </c>
       <c r="K46" t="s">
+        <v>38</v>
+      </c>
+      <c r="L46" t="s">
         <v>39</v>
       </c>
-      <c r="L46" t="s">
-        <v>40</v>
-      </c>
       <c r="M46" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N46" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O46">
         <v>0.56999999999999995</v>
       </c>
       <c r="P46" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q46">
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -8466,28 +8467,28 @@
         <v>24</v>
       </c>
       <c r="K47" t="s">
+        <v>38</v>
+      </c>
+      <c r="L47" t="s">
         <v>39</v>
       </c>
-      <c r="L47" t="s">
-        <v>40</v>
-      </c>
       <c r="M47" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O47">
         <v>0.56699999999999995</v>
       </c>
       <c r="P47" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q47">
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -8519,28 +8520,28 @@
         <v>24</v>
       </c>
       <c r="K48" t="s">
+        <v>38</v>
+      </c>
+      <c r="L48" t="s">
         <v>39</v>
       </c>
-      <c r="L48" t="s">
-        <v>40</v>
-      </c>
       <c r="M48" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N48" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O48">
         <v>0.748</v>
       </c>
       <c r="P48" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q48">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -8572,13 +8573,13 @@
         <v>24</v>
       </c>
       <c r="K49" t="s">
+        <v>40</v>
+      </c>
+      <c r="L49" t="s">
+        <v>41</v>
+      </c>
+      <c r="M49" t="s">
         <v>42</v>
-      </c>
-      <c r="L49" t="s">
-        <v>43</v>
-      </c>
-      <c r="M49" t="s">
-        <v>44</v>
       </c>
       <c r="N49" t="s">
         <v>28</v>
@@ -8587,13 +8588,13 @@
         <v>1.014</v>
       </c>
       <c r="P49" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q49">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -8646,7 +8647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -8693,13 +8694,13 @@
         <v>0.99199999999999999</v>
       </c>
       <c r="P51" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q51">
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -8752,7 +8753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -8790,22 +8791,22 @@
         <v>31</v>
       </c>
       <c r="M53" t="s">
+        <v>80</v>
+      </c>
+      <c r="N53" t="s">
         <v>32</v>
-      </c>
-      <c r="N53" t="s">
-        <v>33</v>
       </c>
       <c r="O53">
         <v>0.69299999999999995</v>
       </c>
       <c r="P53" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q53">
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -8849,7 +8850,7 @@
         <v>28</v>
       </c>
       <c r="O54" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P54" t="s">
         <v>29</v>
@@ -8858,7 +8859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -8890,28 +8891,28 @@
         <v>24</v>
       </c>
       <c r="K55" t="s">
+        <v>38</v>
+      </c>
+      <c r="L55" t="s">
         <v>39</v>
       </c>
-      <c r="L55" t="s">
-        <v>40</v>
-      </c>
       <c r="M55" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N55" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O55">
         <v>0.56399999999999995</v>
       </c>
       <c r="P55" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q55">
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -8943,28 +8944,28 @@
         <v>24</v>
       </c>
       <c r="K56" t="s">
+        <v>34</v>
+      </c>
+      <c r="L56" t="s">
         <v>35</v>
       </c>
-      <c r="L56" t="s">
+      <c r="M56" t="s">
         <v>36</v>
       </c>
-      <c r="M56" t="s">
+      <c r="N56" t="s">
         <v>37</v>
-      </c>
-      <c r="N56" t="s">
-        <v>38</v>
       </c>
       <c r="O56">
         <v>0.26900000000000002</v>
       </c>
       <c r="P56" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q56">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -8996,28 +8997,28 @@
         <v>24</v>
       </c>
       <c r="K57" t="s">
+        <v>38</v>
+      </c>
+      <c r="L57" t="s">
         <v>39</v>
       </c>
-      <c r="L57" t="s">
-        <v>40</v>
-      </c>
       <c r="M57" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N57" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O57">
         <v>0.54900000000000004</v>
       </c>
       <c r="P57" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q57">
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -9061,16 +9062,16 @@
         <v>28</v>
       </c>
       <c r="O58" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P58" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q58">
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -9102,28 +9103,28 @@
         <v>24</v>
       </c>
       <c r="K59" t="s">
+        <v>38</v>
+      </c>
+      <c r="L59" t="s">
         <v>39</v>
       </c>
-      <c r="L59" t="s">
-        <v>40</v>
-      </c>
       <c r="M59" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N59" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O59">
         <v>0.71</v>
       </c>
       <c r="P59" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q59">
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -9155,28 +9156,28 @@
         <v>24</v>
       </c>
       <c r="K60" t="s">
+        <v>38</v>
+      </c>
+      <c r="L60" t="s">
         <v>39</v>
       </c>
-      <c r="L60" t="s">
-        <v>40</v>
-      </c>
       <c r="M60" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N60" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O60">
         <v>0.90100000000000002</v>
       </c>
       <c r="P60" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q60">
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -9220,7 +9221,7 @@
         <v>28</v>
       </c>
       <c r="O61" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P61" t="s">
         <v>29</v>
@@ -9229,7 +9230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -9261,28 +9262,28 @@
         <v>24</v>
       </c>
       <c r="K62" t="s">
+        <v>34</v>
+      </c>
+      <c r="L62" t="s">
         <v>35</v>
       </c>
-      <c r="L62" t="s">
+      <c r="M62" t="s">
         <v>36</v>
       </c>
-      <c r="M62" t="s">
+      <c r="N62" t="s">
         <v>37</v>
-      </c>
-      <c r="N62" t="s">
-        <v>38</v>
       </c>
       <c r="O62">
         <v>0.29399999999999998</v>
       </c>
       <c r="P62" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q62">
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -9314,28 +9315,28 @@
         <v>24</v>
       </c>
       <c r="K63" t="s">
+        <v>34</v>
+      </c>
+      <c r="L63" t="s">
         <v>35</v>
       </c>
-      <c r="L63" t="s">
+      <c r="M63" t="s">
         <v>36</v>
       </c>
-      <c r="M63" t="s">
+      <c r="N63" t="s">
         <v>37</v>
-      </c>
-      <c r="N63" t="s">
-        <v>38</v>
       </c>
       <c r="O63">
         <v>0.29899999999999999</v>
       </c>
       <c r="P63" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q63">
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -9367,13 +9368,13 @@
         <v>24</v>
       </c>
       <c r="K64" t="s">
+        <v>40</v>
+      </c>
+      <c r="L64" t="s">
+        <v>41</v>
+      </c>
+      <c r="M64" t="s">
         <v>42</v>
-      </c>
-      <c r="L64" t="s">
-        <v>43</v>
-      </c>
-      <c r="M64" t="s">
-        <v>44</v>
       </c>
       <c r="N64" t="s">
         <v>28</v>
@@ -9382,13 +9383,13 @@
         <v>0.99</v>
       </c>
       <c r="P64" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q64">
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>18</v>
       </c>
@@ -9420,28 +9421,28 @@
         <v>24</v>
       </c>
       <c r="K65" t="s">
+        <v>34</v>
+      </c>
+      <c r="L65" t="s">
         <v>35</v>
       </c>
-      <c r="L65" t="s">
+      <c r="M65" t="s">
         <v>36</v>
       </c>
-      <c r="M65" t="s">
+      <c r="N65" t="s">
         <v>37</v>
-      </c>
-      <c r="N65" t="s">
-        <v>38</v>
       </c>
       <c r="O65">
         <v>0.251</v>
       </c>
       <c r="P65" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q65">
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -9473,28 +9474,28 @@
         <v>24</v>
       </c>
       <c r="K66" t="s">
+        <v>34</v>
+      </c>
+      <c r="L66" t="s">
         <v>35</v>
       </c>
-      <c r="L66" t="s">
+      <c r="M66" t="s">
         <v>36</v>
       </c>
-      <c r="M66" t="s">
+      <c r="N66" t="s">
         <v>37</v>
-      </c>
-      <c r="N66" t="s">
-        <v>38</v>
       </c>
       <c r="O66">
         <v>0.40500000000000003</v>
       </c>
       <c r="P66" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q66">
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>18</v>
       </c>
@@ -9538,7 +9539,7 @@
         <v>28</v>
       </c>
       <c r="O67" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P67" t="s">
         <v>29</v>
@@ -9547,7 +9548,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -9591,16 +9592,16 @@
         <v>28</v>
       </c>
       <c r="O68" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P68" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q68">
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -9632,28 +9633,28 @@
         <v>24</v>
       </c>
       <c r="K69" t="s">
+        <v>38</v>
+      </c>
+      <c r="L69" t="s">
         <v>39</v>
       </c>
-      <c r="L69" t="s">
-        <v>40</v>
-      </c>
       <c r="M69" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N69" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O69" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P69" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q69">
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -9685,13 +9686,13 @@
         <v>24</v>
       </c>
       <c r="K70" t="s">
+        <v>40</v>
+      </c>
+      <c r="L70" t="s">
+        <v>41</v>
+      </c>
+      <c r="M70" t="s">
         <v>42</v>
-      </c>
-      <c r="L70" t="s">
-        <v>43</v>
-      </c>
-      <c r="M70" t="s">
-        <v>44</v>
       </c>
       <c r="N70" t="s">
         <v>28</v>
@@ -9700,13 +9701,13 @@
         <v>1.101</v>
       </c>
       <c r="P70" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q70">
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -9738,13 +9739,13 @@
         <v>24</v>
       </c>
       <c r="K71" t="s">
+        <v>40</v>
+      </c>
+      <c r="L71" t="s">
+        <v>41</v>
+      </c>
+      <c r="M71" t="s">
         <v>42</v>
-      </c>
-      <c r="L71" t="s">
-        <v>43</v>
-      </c>
-      <c r="M71" t="s">
-        <v>44</v>
       </c>
       <c r="N71" t="s">
         <v>28</v>
@@ -9759,7 +9760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -9791,28 +9792,28 @@
         <v>24</v>
       </c>
       <c r="K72" t="s">
+        <v>34</v>
+      </c>
+      <c r="L72" t="s">
         <v>35</v>
       </c>
-      <c r="L72" t="s">
+      <c r="M72" t="s">
         <v>36</v>
       </c>
-      <c r="M72" t="s">
+      <c r="N72" t="s">
         <v>37</v>
-      </c>
-      <c r="N72" t="s">
-        <v>38</v>
       </c>
       <c r="O72">
         <v>0.27200000000000002</v>
       </c>
       <c r="P72" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q72">
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -9844,13 +9845,13 @@
         <v>24</v>
       </c>
       <c r="K73" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L73" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M73" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N73" t="s">
         <v>28</v>
@@ -9859,13 +9860,13 @@
         <v>1.323</v>
       </c>
       <c r="P73" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q73">
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -9897,28 +9898,28 @@
         <v>24</v>
       </c>
       <c r="K74" t="s">
+        <v>48</v>
+      </c>
+      <c r="L74" t="s">
+        <v>49</v>
+      </c>
+      <c r="M74" t="s">
         <v>50</v>
       </c>
-      <c r="L74" t="s">
-        <v>51</v>
-      </c>
-      <c r="M74" t="s">
-        <v>52</v>
-      </c>
       <c r="N74" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O74">
         <v>0.52800000000000002</v>
       </c>
       <c r="P74" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q74">
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -9950,28 +9951,28 @@
         <v>24</v>
       </c>
       <c r="K75" t="s">
+        <v>48</v>
+      </c>
+      <c r="L75" t="s">
+        <v>49</v>
+      </c>
+      <c r="M75" t="s">
         <v>50</v>
       </c>
-      <c r="L75" t="s">
-        <v>51</v>
-      </c>
-      <c r="M75" t="s">
-        <v>52</v>
-      </c>
       <c r="N75" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O75">
         <v>0.55800000000000005</v>
       </c>
       <c r="P75" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q75">
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -10003,13 +10004,13 @@
         <v>24</v>
       </c>
       <c r="K76" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L76" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M76" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N76" t="s">
         <v>28</v>
@@ -10018,13 +10019,13 @@
         <v>1.1519999999999999</v>
       </c>
       <c r="P76" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q76">
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>18</v>
       </c>
@@ -10056,13 +10057,13 @@
         <v>24</v>
       </c>
       <c r="K77" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L77" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M77" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N77" t="s">
         <v>28</v>
@@ -10077,7 +10078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>18</v>
       </c>
@@ -10109,28 +10110,28 @@
         <v>24</v>
       </c>
       <c r="K78" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L78" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M78" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L78" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M78" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="N78" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O78">
         <v>0.53</v>
       </c>
       <c r="P78" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q78">
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>18</v>
       </c>
@@ -10162,28 +10163,28 @@
         <v>24</v>
       </c>
       <c r="K79" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L79" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M79" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N79" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O79">
         <v>0.81399999999999995</v>
       </c>
       <c r="P79" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q79">
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>18</v>
       </c>
@@ -10215,28 +10216,28 @@
         <v>24</v>
       </c>
       <c r="K80" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M80" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M80" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="N80" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O80">
         <v>0.54900000000000004</v>
       </c>
       <c r="P80" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q80">
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>18</v>
       </c>
@@ -10268,28 +10269,28 @@
         <v>24</v>
       </c>
       <c r="K81" t="s">
+        <v>34</v>
+      </c>
+      <c r="L81" t="s">
         <v>35</v>
       </c>
-      <c r="L81" t="s">
+      <c r="M81" t="s">
         <v>36</v>
       </c>
-      <c r="M81" t="s">
+      <c r="N81" t="s">
         <v>37</v>
-      </c>
-      <c r="N81" t="s">
-        <v>38</v>
       </c>
       <c r="O81">
         <v>0.34399999999999997</v>
       </c>
       <c r="P81" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q81">
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>18</v>
       </c>
@@ -10321,28 +10322,28 @@
         <v>24</v>
       </c>
       <c r="K82" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L82" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M82" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L82" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M82" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="N82" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O82">
         <v>0.76600000000000001</v>
       </c>
       <c r="P82" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q82">
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>18</v>
       </c>
@@ -10374,13 +10375,13 @@
         <v>24</v>
       </c>
       <c r="K83" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L83" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M83" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N83" t="s">
         <v>28</v>
@@ -10395,10 +10396,10 @@
         <v>1</v>
       </c>
       <c r="R83" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>18</v>
       </c>
@@ -10430,28 +10431,28 @@
         <v>24</v>
       </c>
       <c r="K84" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L84" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M84" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L84" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M84" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="N84" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O84">
         <v>0.5</v>
       </c>
       <c r="P84" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q84">
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>18</v>
       </c>
@@ -10483,28 +10484,28 @@
         <v>24</v>
       </c>
       <c r="K85" t="s">
+        <v>34</v>
+      </c>
+      <c r="L85" t="s">
         <v>35</v>
       </c>
-      <c r="L85" t="s">
+      <c r="M85" t="s">
         <v>36</v>
       </c>
-      <c r="M85" t="s">
+      <c r="N85" t="s">
         <v>37</v>
-      </c>
-      <c r="N85" t="s">
-        <v>38</v>
       </c>
       <c r="O85">
         <v>0.34300000000000003</v>
       </c>
       <c r="P85" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q85">
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>18</v>
       </c>
@@ -10536,13 +10537,13 @@
         <v>24</v>
       </c>
       <c r="K86" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L86" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M86" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N86" t="s">
         <v>28</v>
@@ -10557,7 +10558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>18</v>
       </c>
@@ -10589,13 +10590,13 @@
         <v>24</v>
       </c>
       <c r="K87" t="s">
+        <v>40</v>
+      </c>
+      <c r="L87" t="s">
+        <v>41</v>
+      </c>
+      <c r="M87" t="s">
         <v>42</v>
-      </c>
-      <c r="L87" t="s">
-        <v>43</v>
-      </c>
-      <c r="M87" t="s">
-        <v>44</v>
       </c>
       <c r="N87" t="s">
         <v>28</v>
@@ -10610,7 +10611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>18</v>
       </c>
@@ -10642,28 +10643,28 @@
         <v>24</v>
       </c>
       <c r="K88" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L88" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M88" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N88" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O88">
         <v>0.92700000000000005</v>
       </c>
       <c r="P88" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q88">
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>18</v>
       </c>
@@ -10707,7 +10708,7 @@
         <v>28</v>
       </c>
       <c r="O89" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P89" t="s">
         <v>29</v>
@@ -10716,7 +10717,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>18</v>
       </c>
@@ -10760,16 +10761,16 @@
         <v>28</v>
       </c>
       <c r="O90" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P90" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q90">
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>18</v>
       </c>
@@ -10807,22 +10808,22 @@
         <v>31</v>
       </c>
       <c r="M91" t="s">
+        <v>80</v>
+      </c>
+      <c r="N91" t="s">
         <v>32</v>
       </c>
-      <c r="N91" t="s">
-        <v>33</v>
-      </c>
       <c r="O91" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P91" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q91">
         <v>10</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>18</v>
       </c>
@@ -10854,28 +10855,28 @@
         <v>24</v>
       </c>
       <c r="K92" t="s">
+        <v>38</v>
+      </c>
+      <c r="L92" t="s">
         <v>39</v>
       </c>
-      <c r="L92" t="s">
-        <v>40</v>
-      </c>
       <c r="M92" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N92" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O92" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P92" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q92">
         <v>28</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>18</v>
       </c>
@@ -10913,22 +10914,22 @@
         <v>31</v>
       </c>
       <c r="M93" t="s">
+        <v>80</v>
+      </c>
+      <c r="N93" t="s">
         <v>32</v>
-      </c>
-      <c r="N93" t="s">
-        <v>33</v>
       </c>
       <c r="O93">
         <v>0.432</v>
       </c>
       <c r="P93" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q93">
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>18</v>
       </c>
@@ -10966,22 +10967,22 @@
         <v>31</v>
       </c>
       <c r="M94" t="s">
+        <v>80</v>
+      </c>
+      <c r="N94" t="s">
         <v>32</v>
-      </c>
-      <c r="N94" t="s">
-        <v>33</v>
       </c>
       <c r="O94">
         <v>0.872</v>
       </c>
       <c r="P94" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q94">
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>18</v>
       </c>
@@ -11019,22 +11020,22 @@
         <v>31</v>
       </c>
       <c r="M95" t="s">
+        <v>80</v>
+      </c>
+      <c r="N95" t="s">
         <v>32</v>
-      </c>
-      <c r="N95" t="s">
-        <v>33</v>
       </c>
       <c r="O95">
         <v>0.751</v>
       </c>
       <c r="P95" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q95">
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>18</v>
       </c>
@@ -11072,22 +11073,22 @@
         <v>31</v>
       </c>
       <c r="M96" t="s">
+        <v>80</v>
+      </c>
+      <c r="N96" t="s">
         <v>32</v>
-      </c>
-      <c r="N96" t="s">
-        <v>33</v>
       </c>
       <c r="O96">
         <v>0.84299999999999997</v>
       </c>
       <c r="P96" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q96">
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>18</v>
       </c>
@@ -11125,22 +11126,22 @@
         <v>31</v>
       </c>
       <c r="M97" t="s">
+        <v>80</v>
+      </c>
+      <c r="N97" t="s">
         <v>32</v>
-      </c>
-      <c r="N97" t="s">
-        <v>33</v>
       </c>
       <c r="O97">
         <v>0.74199999999999999</v>
       </c>
       <c r="P97" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q97">
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>18</v>
       </c>
@@ -11178,22 +11179,22 @@
         <v>31</v>
       </c>
       <c r="M98" t="s">
+        <v>80</v>
+      </c>
+      <c r="N98" t="s">
         <v>32</v>
-      </c>
-      <c r="N98" t="s">
-        <v>33</v>
       </c>
       <c r="O98">
         <v>0.45200000000000001</v>
       </c>
       <c r="P98" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q98">
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -11225,13 +11226,13 @@
         <v>24</v>
       </c>
       <c r="K99" t="s">
+        <v>40</v>
+      </c>
+      <c r="L99" t="s">
+        <v>41</v>
+      </c>
+      <c r="M99" t="s">
         <v>42</v>
-      </c>
-      <c r="L99" t="s">
-        <v>43</v>
-      </c>
-      <c r="M99" t="s">
-        <v>44</v>
       </c>
       <c r="N99" t="s">
         <v>28</v>
@@ -11240,13 +11241,13 @@
         <v>1.1659999999999999</v>
       </c>
       <c r="P99" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q99">
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>18</v>
       </c>
@@ -11284,22 +11285,22 @@
         <v>31</v>
       </c>
       <c r="M100" t="s">
+        <v>80</v>
+      </c>
+      <c r="N100" t="s">
         <v>32</v>
-      </c>
-      <c r="N100" t="s">
-        <v>33</v>
       </c>
       <c r="O100">
         <v>0.82</v>
       </c>
       <c r="P100" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q100">
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>18</v>
       </c>
@@ -11331,28 +11332,28 @@
         <v>24</v>
       </c>
       <c r="K101" t="s">
+        <v>34</v>
+      </c>
+      <c r="L101" t="s">
         <v>35</v>
       </c>
-      <c r="L101" t="s">
+      <c r="M101" t="s">
         <v>36</v>
       </c>
-      <c r="M101" t="s">
+      <c r="N101" t="s">
         <v>37</v>
-      </c>
-      <c r="N101" t="s">
-        <v>38</v>
       </c>
       <c r="O101">
         <v>0.28199999999999997</v>
       </c>
       <c r="P101" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q101">
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>18</v>
       </c>
@@ -11390,22 +11391,22 @@
         <v>31</v>
       </c>
       <c r="M102" t="s">
+        <v>80</v>
+      </c>
+      <c r="N102" t="s">
         <v>32</v>
-      </c>
-      <c r="N102" t="s">
-        <v>33</v>
       </c>
       <c r="O102">
         <v>0.84299999999999997</v>
       </c>
       <c r="P102" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q102">
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>18</v>
       </c>
@@ -11437,28 +11438,28 @@
         <v>24</v>
       </c>
       <c r="K103" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L103" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M103" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N103" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O103">
         <v>0.81499999999999995</v>
       </c>
       <c r="P103" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q103">
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>18</v>
       </c>
@@ -11496,22 +11497,22 @@
         <v>31</v>
       </c>
       <c r="M104" t="s">
+        <v>80</v>
+      </c>
+      <c r="N104" t="s">
         <v>32</v>
-      </c>
-      <c r="N104" t="s">
-        <v>33</v>
       </c>
       <c r="O104">
         <v>0.79100000000000004</v>
       </c>
       <c r="P104" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q104">
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>18</v>
       </c>
@@ -11543,28 +11544,28 @@
         <v>24</v>
       </c>
       <c r="K105" t="s">
+        <v>34</v>
+      </c>
+      <c r="L105" t="s">
         <v>35</v>
       </c>
-      <c r="L105" t="s">
+      <c r="M105" t="s">
         <v>36</v>
       </c>
-      <c r="M105" t="s">
+      <c r="N105" t="s">
         <v>37</v>
-      </c>
-      <c r="N105" t="s">
-        <v>38</v>
       </c>
       <c r="O105">
         <v>0.30499999999999999</v>
       </c>
       <c r="P105" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q105">
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>18</v>
       </c>
@@ -11596,28 +11597,28 @@
         <v>24</v>
       </c>
       <c r="K106" t="s">
+        <v>34</v>
+      </c>
+      <c r="L106" t="s">
         <v>35</v>
       </c>
-      <c r="L106" t="s">
+      <c r="M106" t="s">
         <v>36</v>
       </c>
-      <c r="M106" t="s">
+      <c r="N106" t="s">
         <v>37</v>
-      </c>
-      <c r="N106" t="s">
-        <v>38</v>
       </c>
       <c r="O106">
         <v>0.30599999999999999</v>
       </c>
       <c r="P106" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q106">
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>18</v>
       </c>
@@ -11655,22 +11656,22 @@
         <v>31</v>
       </c>
       <c r="M107" t="s">
+        <v>80</v>
+      </c>
+      <c r="N107" t="s">
         <v>32</v>
-      </c>
-      <c r="N107" t="s">
-        <v>33</v>
       </c>
       <c r="O107">
         <v>0.875</v>
       </c>
       <c r="P107" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q107">
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>18</v>
       </c>
@@ -11708,22 +11709,22 @@
         <v>31</v>
       </c>
       <c r="M108" t="s">
+        <v>80</v>
+      </c>
+      <c r="N108" t="s">
         <v>32</v>
-      </c>
-      <c r="N108" t="s">
-        <v>33</v>
       </c>
       <c r="O108">
         <v>0.94899999999999995</v>
       </c>
       <c r="P108" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q108">
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>18</v>
       </c>
@@ -11755,28 +11756,28 @@
         <v>24</v>
       </c>
       <c r="K109" t="s">
+        <v>34</v>
+      </c>
+      <c r="L109" t="s">
         <v>35</v>
       </c>
-      <c r="L109" t="s">
+      <c r="M109" t="s">
         <v>36</v>
       </c>
-      <c r="M109" t="s">
+      <c r="N109" t="s">
         <v>37</v>
-      </c>
-      <c r="N109" t="s">
-        <v>38</v>
       </c>
       <c r="O109">
         <v>0.26300000000000001</v>
       </c>
       <c r="P109" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q109">
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>18</v>
       </c>
@@ -11808,28 +11809,28 @@
         <v>24</v>
       </c>
       <c r="K110" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L110" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="M110" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N110" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O110">
         <v>0.504</v>
       </c>
       <c r="P110" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q110">
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>18</v>
       </c>
@@ -11861,13 +11862,13 @@
         <v>24</v>
       </c>
       <c r="K111" t="s">
+        <v>40</v>
+      </c>
+      <c r="L111" t="s">
+        <v>41</v>
+      </c>
+      <c r="M111" t="s">
         <v>42</v>
-      </c>
-      <c r="L111" t="s">
-        <v>43</v>
-      </c>
-      <c r="M111" t="s">
-        <v>44</v>
       </c>
       <c r="N111" t="s">
         <v>28</v>
@@ -11882,7 +11883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>18</v>
       </c>
@@ -11914,28 +11915,28 @@
         <v>24</v>
       </c>
       <c r="K112" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L112" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M112" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L112" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M112" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="N112" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O112">
         <v>0.67400000000000004</v>
       </c>
       <c r="P112" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q112">
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>18</v>
       </c>
@@ -11967,28 +11968,28 @@
         <v>24</v>
       </c>
       <c r="K113" t="s">
+        <v>34</v>
+      </c>
+      <c r="L113" t="s">
         <v>35</v>
       </c>
-      <c r="L113" t="s">
+      <c r="M113" t="s">
         <v>36</v>
       </c>
-      <c r="M113" t="s">
+      <c r="N113" t="s">
         <v>37</v>
-      </c>
-      <c r="N113" t="s">
-        <v>38</v>
       </c>
       <c r="O113">
         <v>0.53300000000000003</v>
       </c>
       <c r="P113" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q113">
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>18</v>
       </c>
@@ -12020,28 +12021,28 @@
         <v>24</v>
       </c>
       <c r="K114" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L114" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M114" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N114" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O114">
         <v>0.76300000000000001</v>
       </c>
       <c r="P114" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q114">
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>18</v>
       </c>
@@ -12073,28 +12074,28 @@
         <v>24</v>
       </c>
       <c r="K115" t="s">
+        <v>48</v>
+      </c>
+      <c r="L115" t="s">
+        <v>49</v>
+      </c>
+      <c r="M115" t="s">
         <v>50</v>
       </c>
-      <c r="L115" t="s">
-        <v>51</v>
-      </c>
-      <c r="M115" t="s">
-        <v>52</v>
-      </c>
       <c r="N115" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O115">
         <v>0.45800000000000002</v>
       </c>
       <c r="P115" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q115">
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>18</v>
       </c>
@@ -12126,13 +12127,13 @@
         <v>24</v>
       </c>
       <c r="K116" t="s">
+        <v>40</v>
+      </c>
+      <c r="L116" t="s">
+        <v>41</v>
+      </c>
+      <c r="M116" t="s">
         <v>42</v>
-      </c>
-      <c r="L116" t="s">
-        <v>43</v>
-      </c>
-      <c r="M116" t="s">
-        <v>44</v>
       </c>
       <c r="N116" t="s">
         <v>28</v>
@@ -12147,7 +12148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>18</v>
       </c>
@@ -12179,28 +12180,28 @@
         <v>24</v>
       </c>
       <c r="K117" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L117" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M117" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N117" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O117">
         <v>0.98099999999999998</v>
       </c>
       <c r="P117" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q117">
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>18</v>
       </c>
@@ -12232,28 +12233,28 @@
         <v>24</v>
       </c>
       <c r="K118" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L118" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M118" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N118" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O118">
         <v>0.65600000000000003</v>
       </c>
       <c r="P118" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q118">
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>18</v>
       </c>
@@ -12285,13 +12286,13 @@
         <v>24</v>
       </c>
       <c r="K119" t="s">
+        <v>40</v>
+      </c>
+      <c r="L119" t="s">
+        <v>41</v>
+      </c>
+      <c r="M119" t="s">
         <v>42</v>
-      </c>
-      <c r="L119" t="s">
-        <v>43</v>
-      </c>
-      <c r="M119" t="s">
-        <v>44</v>
       </c>
       <c r="N119" t="s">
         <v>28</v>
@@ -12300,13 +12301,13 @@
         <v>1.099</v>
       </c>
       <c r="P119" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q119">
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>18</v>
       </c>
@@ -12338,13 +12339,13 @@
         <v>24</v>
       </c>
       <c r="K120" t="s">
+        <v>40</v>
+      </c>
+      <c r="L120" t="s">
+        <v>41</v>
+      </c>
+      <c r="M120" t="s">
         <v>42</v>
-      </c>
-      <c r="L120" t="s">
-        <v>43</v>
-      </c>
-      <c r="M120" t="s">
-        <v>44</v>
       </c>
       <c r="N120" t="s">
         <v>28</v>
@@ -12359,7 +12360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>18</v>
       </c>
@@ -12403,7 +12404,7 @@
         <v>28</v>
       </c>
       <c r="O121" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P121" t="s">
         <v>29</v>
@@ -12412,7 +12413,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>18</v>
       </c>
@@ -12456,16 +12457,16 @@
         <v>28</v>
       </c>
       <c r="O122" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P122" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q122">
         <v>8</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>18</v>
       </c>
@@ -12503,22 +12504,22 @@
         <v>31</v>
       </c>
       <c r="M123" t="s">
+        <v>80</v>
+      </c>
+      <c r="N123" t="s">
         <v>32</v>
       </c>
-      <c r="N123" t="s">
-        <v>33</v>
-      </c>
       <c r="O123" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P123" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q123">
         <v>8</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>18</v>
       </c>
@@ -12550,28 +12551,28 @@
         <v>24</v>
       </c>
       <c r="K124" t="s">
+        <v>38</v>
+      </c>
+      <c r="L124" t="s">
         <v>39</v>
       </c>
-      <c r="L124" t="s">
-        <v>40</v>
-      </c>
       <c r="M124" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N124" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O124" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P124" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q124">
         <v>26</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>18</v>
       </c>
@@ -12603,28 +12604,28 @@
         <v>24</v>
       </c>
       <c r="K125" t="s">
+        <v>34</v>
+      </c>
+      <c r="L125" t="s">
         <v>35</v>
       </c>
-      <c r="L125" t="s">
+      <c r="M125" t="s">
         <v>36</v>
       </c>
-      <c r="M125" t="s">
+      <c r="N125" t="s">
         <v>37</v>
-      </c>
-      <c r="N125" t="s">
-        <v>38</v>
       </c>
       <c r="O125">
         <v>0.30399999999999999</v>
       </c>
       <c r="P125" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q125">
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>18</v>
       </c>
@@ -12656,13 +12657,13 @@
         <v>24</v>
       </c>
       <c r="K126" t="s">
+        <v>40</v>
+      </c>
+      <c r="L126" t="s">
+        <v>41</v>
+      </c>
+      <c r="M126" t="s">
         <v>42</v>
-      </c>
-      <c r="L126" t="s">
-        <v>43</v>
-      </c>
-      <c r="M126" t="s">
-        <v>44</v>
       </c>
       <c r="N126" t="s">
         <v>28</v>
@@ -12671,13 +12672,13 @@
         <v>1.0309999999999999</v>
       </c>
       <c r="P126" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q126">
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>18</v>
       </c>
@@ -12709,13 +12710,13 @@
         <v>24</v>
       </c>
       <c r="K127" t="s">
+        <v>40</v>
+      </c>
+      <c r="L127" t="s">
+        <v>41</v>
+      </c>
+      <c r="M127" t="s">
         <v>42</v>
-      </c>
-      <c r="L127" t="s">
-        <v>43</v>
-      </c>
-      <c r="M127" t="s">
-        <v>44</v>
       </c>
       <c r="N127" t="s">
         <v>28</v>
@@ -12730,7 +12731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>18</v>
       </c>
@@ -12762,28 +12763,28 @@
         <v>24</v>
       </c>
       <c r="K128" t="s">
+        <v>34</v>
+      </c>
+      <c r="L128" t="s">
         <v>35</v>
       </c>
-      <c r="L128" t="s">
+      <c r="M128" t="s">
         <v>36</v>
       </c>
-      <c r="M128" t="s">
+      <c r="N128" t="s">
         <v>37</v>
-      </c>
-      <c r="N128" t="s">
-        <v>38</v>
       </c>
       <c r="O128">
         <v>0.28699999999999998</v>
       </c>
       <c r="P128" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q128">
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>18</v>
       </c>
@@ -12815,28 +12816,28 @@
         <v>24</v>
       </c>
       <c r="K129" t="s">
+        <v>34</v>
+      </c>
+      <c r="L129" t="s">
         <v>35</v>
       </c>
-      <c r="L129" t="s">
+      <c r="M129" t="s">
         <v>36</v>
       </c>
-      <c r="M129" t="s">
+      <c r="N129" t="s">
         <v>37</v>
-      </c>
-      <c r="N129" t="s">
-        <v>38</v>
       </c>
       <c r="O129">
         <v>0.30299999999999999</v>
       </c>
       <c r="P129" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q129">
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>18</v>
       </c>
@@ -12868,13 +12869,13 @@
         <v>24</v>
       </c>
       <c r="K130" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L130" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M130" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N130" t="s">
         <v>28</v>
@@ -12883,13 +12884,13 @@
         <v>1.1160000000000001</v>
       </c>
       <c r="P130" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q130">
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>18</v>
       </c>
@@ -12921,28 +12922,28 @@
         <v>24</v>
       </c>
       <c r="K131" t="s">
+        <v>34</v>
+      </c>
+      <c r="L131" t="s">
         <v>35</v>
       </c>
-      <c r="L131" t="s">
+      <c r="M131" t="s">
         <v>36</v>
       </c>
-      <c r="M131" t="s">
+      <c r="N131" t="s">
         <v>37</v>
-      </c>
-      <c r="N131" t="s">
-        <v>38</v>
       </c>
       <c r="O131">
         <v>0.3</v>
       </c>
       <c r="P131" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q131">
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>18</v>
       </c>
@@ -12974,13 +12975,13 @@
         <v>24</v>
       </c>
       <c r="K132" t="s">
+        <v>40</v>
+      </c>
+      <c r="L132" t="s">
+        <v>41</v>
+      </c>
+      <c r="M132" t="s">
         <v>42</v>
-      </c>
-      <c r="L132" t="s">
-        <v>43</v>
-      </c>
-      <c r="M132" t="s">
-        <v>44</v>
       </c>
       <c r="N132" t="s">
         <v>28</v>
@@ -12989,13 +12990,13 @@
         <v>1.0620000000000001</v>
       </c>
       <c r="P132" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q132">
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>18</v>
       </c>
@@ -13027,28 +13028,28 @@
         <v>24</v>
       </c>
       <c r="K133" t="s">
+        <v>34</v>
+      </c>
+      <c r="L133" t="s">
         <v>35</v>
       </c>
-      <c r="L133" t="s">
+      <c r="M133" t="s">
         <v>36</v>
       </c>
-      <c r="M133" t="s">
+      <c r="N133" t="s">
         <v>37</v>
-      </c>
-      <c r="N133" t="s">
-        <v>38</v>
       </c>
       <c r="O133">
         <v>0.30199999999999999</v>
       </c>
       <c r="P133" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q133">
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>18</v>
       </c>
@@ -13080,28 +13081,28 @@
         <v>24</v>
       </c>
       <c r="K134" t="s">
+        <v>34</v>
+      </c>
+      <c r="L134" t="s">
         <v>35</v>
       </c>
-      <c r="L134" t="s">
+      <c r="M134" t="s">
         <v>36</v>
       </c>
-      <c r="M134" t="s">
+      <c r="N134" t="s">
         <v>37</v>
-      </c>
-      <c r="N134" t="s">
-        <v>38</v>
       </c>
       <c r="O134">
         <v>0.307</v>
       </c>
       <c r="P134" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q134">
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>18</v>
       </c>
@@ -13133,28 +13134,28 @@
         <v>24</v>
       </c>
       <c r="K135" t="s">
+        <v>48</v>
+      </c>
+      <c r="L135" t="s">
+        <v>49</v>
+      </c>
+      <c r="M135" t="s">
         <v>50</v>
       </c>
-      <c r="L135" t="s">
-        <v>51</v>
-      </c>
-      <c r="M135" t="s">
-        <v>52</v>
-      </c>
       <c r="N135" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O135">
         <v>0.29399999999999998</v>
       </c>
       <c r="P135" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q135">
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>18</v>
       </c>
@@ -13186,13 +13187,13 @@
         <v>24</v>
       </c>
       <c r="K136" t="s">
+        <v>40</v>
+      </c>
+      <c r="L136" t="s">
+        <v>41</v>
+      </c>
+      <c r="M136" t="s">
         <v>42</v>
-      </c>
-      <c r="L136" t="s">
-        <v>43</v>
-      </c>
-      <c r="M136" t="s">
-        <v>44</v>
       </c>
       <c r="N136" t="s">
         <v>28</v>
@@ -13201,13 +13202,13 @@
         <v>1.1140000000000001</v>
       </c>
       <c r="P136" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q136">
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>18</v>
       </c>
@@ -13239,28 +13240,28 @@
         <v>24</v>
       </c>
       <c r="K137" t="s">
+        <v>48</v>
+      </c>
+      <c r="L137" t="s">
+        <v>49</v>
+      </c>
+      <c r="M137" t="s">
         <v>50</v>
       </c>
-      <c r="L137" t="s">
-        <v>51</v>
-      </c>
-      <c r="M137" t="s">
-        <v>52</v>
-      </c>
       <c r="N137" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O137">
         <v>0.82799999999999996</v>
       </c>
       <c r="P137" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q137">
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>18</v>
       </c>
@@ -13304,7 +13305,7 @@
         <v>28</v>
       </c>
       <c r="O138" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P138" t="s">
         <v>29</v>
@@ -13313,7 +13314,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>18</v>
       </c>
@@ -13357,16 +13358,16 @@
         <v>28</v>
       </c>
       <c r="O139" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P139" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q139">
         <v>7</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>18</v>
       </c>
@@ -13404,22 +13405,22 @@
         <v>31</v>
       </c>
       <c r="M140" t="s">
+        <v>80</v>
+      </c>
+      <c r="N140" t="s">
         <v>32</v>
       </c>
-      <c r="N140" t="s">
-        <v>33</v>
-      </c>
       <c r="O140" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P140" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q140">
         <v>13</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>18</v>
       </c>
@@ -13451,28 +13452,28 @@
         <v>24</v>
       </c>
       <c r="K141" t="s">
+        <v>38</v>
+      </c>
+      <c r="L141" t="s">
         <v>39</v>
       </c>
-      <c r="L141" t="s">
-        <v>40</v>
-      </c>
       <c r="M141" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N141" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O141" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P141" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q141">
         <v>25</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>18</v>
       </c>
@@ -13504,28 +13505,28 @@
         <v>24</v>
       </c>
       <c r="K142" t="s">
+        <v>34</v>
+      </c>
+      <c r="L142" t="s">
         <v>35</v>
       </c>
-      <c r="L142" t="s">
+      <c r="M142" t="s">
         <v>36</v>
       </c>
-      <c r="M142" t="s">
+      <c r="N142" t="s">
         <v>37</v>
       </c>
-      <c r="N142" t="s">
-        <v>38</v>
-      </c>
       <c r="O142" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P142" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q142">
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>18</v>
       </c>
@@ -13557,28 +13558,28 @@
         <v>24</v>
       </c>
       <c r="K143" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L143" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M143" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L143" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M143" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="N143" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O143">
         <v>0.49</v>
       </c>
       <c r="P143" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q143">
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>18</v>
       </c>
@@ -13610,13 +13611,13 @@
         <v>24</v>
       </c>
       <c r="K144" t="s">
+        <v>40</v>
+      </c>
+      <c r="L144" t="s">
+        <v>41</v>
+      </c>
+      <c r="M144" t="s">
         <v>42</v>
-      </c>
-      <c r="L144" t="s">
-        <v>43</v>
-      </c>
-      <c r="M144" t="s">
-        <v>44</v>
       </c>
       <c r="N144" t="s">
         <v>28</v>
@@ -13625,13 +13626,13 @@
         <v>1.052</v>
       </c>
       <c r="P144" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q144">
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>18</v>
       </c>
@@ -13663,16 +13664,16 @@
         <v>24</v>
       </c>
       <c r="K145" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L145" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M145" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N145" s="3" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="O145">
         <v>1.242</v>
@@ -13684,7 +13685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>18</v>
       </c>
@@ -13716,16 +13717,16 @@
         <v>24</v>
       </c>
       <c r="K146" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L146" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M146" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N146" s="3" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="O146">
         <v>1.048</v>
@@ -13737,7 +13738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>18</v>
       </c>
@@ -13781,7 +13782,7 @@
         <v>28</v>
       </c>
       <c r="O147" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P147" t="s">
         <v>29</v>
@@ -13790,7 +13791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>18</v>
       </c>
@@ -13828,22 +13829,22 @@
         <v>31</v>
       </c>
       <c r="M148" t="s">
+        <v>80</v>
+      </c>
+      <c r="N148" t="s">
         <v>32</v>
       </c>
-      <c r="N148" t="s">
-        <v>33</v>
-      </c>
       <c r="O148" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P148" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q148">
         <v>5</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>18</v>
       </c>
@@ -13875,28 +13876,28 @@
         <v>24</v>
       </c>
       <c r="K149" t="s">
+        <v>38</v>
+      </c>
+      <c r="L149" t="s">
         <v>39</v>
       </c>
-      <c r="L149" t="s">
-        <v>40</v>
-      </c>
       <c r="M149" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N149" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O149" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P149" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q149">
         <v>3</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>18</v>
       </c>
@@ -13928,28 +13929,28 @@
         <v>24</v>
       </c>
       <c r="K150" t="s">
+        <v>34</v>
+      </c>
+      <c r="L150" t="s">
         <v>35</v>
       </c>
-      <c r="L150" t="s">
+      <c r="M150" t="s">
         <v>36</v>
       </c>
-      <c r="M150" t="s">
+      <c r="N150" t="s">
         <v>37</v>
       </c>
-      <c r="N150" t="s">
-        <v>38</v>
-      </c>
       <c r="O150" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P150" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q150">
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>18</v>
       </c>
@@ -13963,7 +13964,7 @@
         <v>-1</v>
       </c>
       <c r="E151" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F151">
         <v>64</v>
@@ -13981,13 +13982,13 @@
         <v>24</v>
       </c>
       <c r="K151" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L151" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M151" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N151" t="s">
         <v>28</v>
@@ -14002,7 +14003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>18</v>
       </c>
@@ -14016,7 +14017,7 @@
         <v>-1</v>
       </c>
       <c r="E152" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F152">
         <v>64</v>
@@ -14034,13 +14035,13 @@
         <v>24</v>
       </c>
       <c r="K152" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L152" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M152" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N152" t="s">
         <v>28</v>
@@ -14055,7 +14056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>18</v>
       </c>
@@ -14069,7 +14070,7 @@
         <v>-1</v>
       </c>
       <c r="E153" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F153">
         <v>64</v>
@@ -14087,13 +14088,13 @@
         <v>24</v>
       </c>
       <c r="K153" t="s">
+        <v>40</v>
+      </c>
+      <c r="L153" t="s">
+        <v>41</v>
+      </c>
+      <c r="M153" t="s">
         <v>42</v>
-      </c>
-      <c r="L153" t="s">
-        <v>43</v>
-      </c>
-      <c r="M153" t="s">
-        <v>44</v>
       </c>
       <c r="N153" t="s">
         <v>28</v>
@@ -14102,13 +14103,13 @@
         <v>0.997</v>
       </c>
       <c r="P153" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q153">
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>18</v>
       </c>
@@ -14122,7 +14123,7 @@
         <v>-1</v>
       </c>
       <c r="E154" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F154">
         <v>64</v>
@@ -14140,13 +14141,13 @@
         <v>24</v>
       </c>
       <c r="K154" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L154" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M154" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N154" t="s">
         <v>28</v>
@@ -14161,7 +14162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>18</v>
       </c>
@@ -14175,7 +14176,7 @@
         <v>-1</v>
       </c>
       <c r="E155" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F155">
         <v>64</v>
@@ -14193,28 +14194,28 @@
         <v>24</v>
       </c>
       <c r="K155" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L155" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M155" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N155" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O155">
         <v>0.99399999999999999</v>
       </c>
       <c r="P155" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q155">
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>18</v>
       </c>
@@ -14228,7 +14229,7 @@
         <v>-1</v>
       </c>
       <c r="E156" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F156">
         <v>64</v>
@@ -14246,28 +14247,28 @@
         <v>24</v>
       </c>
       <c r="K156" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L156" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M156" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N156" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O156">
         <v>0.91600000000000004</v>
       </c>
       <c r="P156" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q156">
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>18</v>
       </c>
@@ -14281,7 +14282,7 @@
         <v>-1</v>
       </c>
       <c r="E157" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F157">
         <v>64</v>
@@ -14299,28 +14300,28 @@
         <v>24</v>
       </c>
       <c r="K157" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L157" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M157" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L157" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M157" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="N157" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O157">
         <v>0.57399999999999995</v>
       </c>
       <c r="P157" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q157">
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>18</v>
       </c>
@@ -14334,7 +14335,7 @@
         <v>-1</v>
       </c>
       <c r="E158" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F158">
         <v>64</v>
@@ -14352,28 +14353,28 @@
         <v>24</v>
       </c>
       <c r="K158" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L158" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M158" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L158" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M158" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="N158" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O158">
         <v>0.58899999999999997</v>
       </c>
       <c r="P158" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q158">
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>18</v>
       </c>
@@ -14387,7 +14388,7 @@
         <v>-1</v>
       </c>
       <c r="E159" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F159">
         <v>64</v>
@@ -14405,28 +14406,28 @@
         <v>24</v>
       </c>
       <c r="K159" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L159" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M159" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N159" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O159">
         <v>0.82</v>
       </c>
       <c r="P159" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q159">
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>18</v>
       </c>
@@ -14440,7 +14441,7 @@
         <v>-1</v>
       </c>
       <c r="E160" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F160">
         <v>64</v>
@@ -14458,28 +14459,28 @@
         <v>24</v>
       </c>
       <c r="K160" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L160" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M160" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N160" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O160">
         <v>0.58499999999999996</v>
       </c>
       <c r="P160" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q160">
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>18</v>
       </c>
@@ -14493,7 +14494,7 @@
         <v>-1</v>
       </c>
       <c r="E161" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F161">
         <v>64</v>
@@ -14511,13 +14512,13 @@
         <v>24</v>
       </c>
       <c r="K161" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L161" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M161" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N161" t="s">
         <v>28</v>
@@ -14532,7 +14533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>18</v>
       </c>
@@ -14546,7 +14547,7 @@
         <v>-1</v>
       </c>
       <c r="E162" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F162">
         <v>64</v>
@@ -14564,28 +14565,28 @@
         <v>24</v>
       </c>
       <c r="K162" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L162" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M162" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L162" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M162" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="N162" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O162">
         <v>0.57199999999999995</v>
       </c>
       <c r="P162" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q162">
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>18</v>
       </c>
@@ -14599,7 +14600,7 @@
         <v>-1</v>
       </c>
       <c r="E163" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F163">
         <v>64</v>
@@ -14617,28 +14618,28 @@
         <v>24</v>
       </c>
       <c r="K163" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L163" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M163" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N163" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O163">
         <v>0.77100000000000002</v>
       </c>
       <c r="P163" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q163">
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>18</v>
       </c>
@@ -14652,7 +14653,7 @@
         <v>-1</v>
       </c>
       <c r="E164" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F164">
         <v>64</v>
@@ -14670,13 +14671,13 @@
         <v>24</v>
       </c>
       <c r="K164" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L164" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M164" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N164" t="s">
         <v>28</v>
@@ -14691,7 +14692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>18</v>
       </c>
@@ -14705,7 +14706,7 @@
         <v>-1</v>
       </c>
       <c r="E165" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F165">
         <v>64</v>
@@ -14723,28 +14724,28 @@
         <v>24</v>
       </c>
       <c r="K165" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L165" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M165" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L165" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M165" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="N165" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O165">
         <v>0.56100000000000005</v>
       </c>
       <c r="P165" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q165">
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>18</v>
       </c>
@@ -14758,7 +14759,7 @@
         <v>-1</v>
       </c>
       <c r="E166" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F166">
         <v>64</v>
@@ -14776,28 +14777,28 @@
         <v>24</v>
       </c>
       <c r="K166" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L166" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M166" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L166" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M166" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="N166" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O166">
         <v>0.41699999999999998</v>
       </c>
       <c r="P166" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q166">
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>18</v>
       </c>
@@ -14811,7 +14812,7 @@
         <v>-1</v>
       </c>
       <c r="E167" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F167">
         <v>64</v>
@@ -14829,28 +14830,28 @@
         <v>24</v>
       </c>
       <c r="K167" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L167" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M167" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L167" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M167" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="N167" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O167">
         <v>0.753</v>
       </c>
       <c r="P167" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q167">
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>18</v>
       </c>
@@ -14864,7 +14865,7 @@
         <v>-1</v>
       </c>
       <c r="E168" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F168">
         <v>64</v>
@@ -14882,28 +14883,28 @@
         <v>24</v>
       </c>
       <c r="K168" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L168" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M168" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L168" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M168" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="N168" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O168">
         <v>0.65600000000000003</v>
       </c>
       <c r="P168" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q168">
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>18</v>
       </c>
@@ -14917,7 +14918,7 @@
         <v>-1</v>
       </c>
       <c r="E169" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F169">
         <v>64</v>
@@ -14935,13 +14936,13 @@
         <v>24</v>
       </c>
       <c r="K169" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L169" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M169" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N169" t="s">
         <v>28</v>
@@ -14956,7 +14957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>18</v>
       </c>
@@ -14970,7 +14971,7 @@
         <v>-1</v>
       </c>
       <c r="E170" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F170">
         <v>64</v>
@@ -14988,13 +14989,13 @@
         <v>24</v>
       </c>
       <c r="K170" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L170" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M170" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N170" t="s">
         <v>28</v>
@@ -15003,13 +15004,13 @@
         <v>1.3420000000000001</v>
       </c>
       <c r="P170" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q170">
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>18</v>
       </c>
@@ -15023,7 +15024,7 @@
         <v>-1</v>
       </c>
       <c r="E171" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F171">
         <v>64</v>
@@ -15041,28 +15042,28 @@
         <v>24</v>
       </c>
       <c r="K171" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L171" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M171" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N171" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O171">
         <v>0.91200000000000003</v>
       </c>
       <c r="P171" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q171">
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>18</v>
       </c>
@@ -15076,7 +15077,7 @@
         <v>-1</v>
       </c>
       <c r="E172" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F172">
         <v>64</v>
@@ -15094,28 +15095,28 @@
         <v>24</v>
       </c>
       <c r="K172" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L172" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M172" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N172" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O172">
         <v>1.216</v>
       </c>
       <c r="P172" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q172">
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>18</v>
       </c>
@@ -15129,7 +15130,7 @@
         <v>-1</v>
       </c>
       <c r="E173" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F173">
         <v>64</v>
@@ -15147,13 +15148,13 @@
         <v>24</v>
       </c>
       <c r="K173" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L173" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M173" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N173" t="s">
         <v>28</v>
@@ -15168,7 +15169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>18</v>
       </c>
@@ -15182,7 +15183,7 @@
         <v>-1</v>
       </c>
       <c r="E174" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F174">
         <v>64</v>
@@ -15200,28 +15201,28 @@
         <v>24</v>
       </c>
       <c r="K174" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L174" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M174" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L174" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M174" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="N174" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O174">
         <v>0.78</v>
       </c>
       <c r="P174" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q174">
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>18</v>
       </c>
@@ -15235,7 +15236,7 @@
         <v>-1</v>
       </c>
       <c r="E175" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F175">
         <v>64</v>
@@ -15253,19 +15254,19 @@
         <v>24</v>
       </c>
       <c r="K175" t="s">
+        <v>40</v>
+      </c>
+      <c r="L175" t="s">
+        <v>41</v>
+      </c>
+      <c r="M175" t="s">
         <v>42</v>
-      </c>
-      <c r="L175" t="s">
-        <v>43</v>
-      </c>
-      <c r="M175" t="s">
-        <v>44</v>
       </c>
       <c r="N175" t="s">
         <v>28</v>
       </c>
       <c r="O175" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P175" t="s">
         <v>29</v>
@@ -15274,7 +15275,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>18</v>
       </c>
@@ -15288,7 +15289,7 @@
         <v>-1</v>
       </c>
       <c r="E176" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F176">
         <v>64</v>
@@ -15306,28 +15307,28 @@
         <v>24</v>
       </c>
       <c r="K176" t="s">
+        <v>40</v>
+      </c>
+      <c r="L176" t="s">
+        <v>41</v>
+      </c>
+      <c r="M176" t="s">
         <v>42</v>
-      </c>
-      <c r="L176" t="s">
-        <v>43</v>
-      </c>
-      <c r="M176" t="s">
-        <v>44</v>
       </c>
       <c r="N176" t="s">
         <v>28</v>
       </c>
       <c r="O176" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P176" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q176">
         <v>8</v>
       </c>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>18</v>
       </c>
@@ -15341,7 +15342,7 @@
         <v>-1</v>
       </c>
       <c r="E177" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F177">
         <v>64</v>
@@ -15359,28 +15360,28 @@
         <v>24</v>
       </c>
       <c r="K177" t="s">
+        <v>34</v>
+      </c>
+      <c r="L177" t="s">
         <v>35</v>
       </c>
-      <c r="L177" t="s">
+      <c r="M177" t="s">
         <v>36</v>
       </c>
-      <c r="M177" t="s">
+      <c r="N177" t="s">
         <v>37</v>
       </c>
-      <c r="N177" t="s">
-        <v>38</v>
-      </c>
       <c r="O177" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P177" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q177">
         <v>26</v>
       </c>
     </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>18</v>
       </c>
@@ -15394,7 +15395,7 @@
         <v>-1</v>
       </c>
       <c r="E178" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F178">
         <v>64</v>
@@ -15424,7 +15425,7 @@
         <v>28</v>
       </c>
       <c r="O178" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P178" t="s">
         <v>29</v>
@@ -15433,7 +15434,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>18</v>
       </c>
@@ -15447,7 +15448,7 @@
         <v>-1</v>
       </c>
       <c r="E179" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F179">
         <v>64</v>
@@ -15477,16 +15478,16 @@
         <v>28</v>
       </c>
       <c r="O179" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P179" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q179">
         <v>43</v>
       </c>
     </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>18</v>
       </c>
@@ -15500,7 +15501,7 @@
         <v>-1</v>
       </c>
       <c r="E180" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F180">
         <v>64</v>
@@ -15524,22 +15525,22 @@
         <v>31</v>
       </c>
       <c r="M180" t="s">
+        <v>80</v>
+      </c>
+      <c r="N180" t="s">
         <v>32</v>
       </c>
-      <c r="N180" t="s">
-        <v>33</v>
-      </c>
       <c r="O180" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P180" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q180">
         <v>77</v>
       </c>
     </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>18</v>
       </c>
@@ -15553,7 +15554,7 @@
         <v>-1</v>
       </c>
       <c r="E181" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F181">
         <v>64</v>
@@ -15571,28 +15572,28 @@
         <v>24</v>
       </c>
       <c r="K181" t="s">
+        <v>38</v>
+      </c>
+      <c r="L181" t="s">
         <v>39</v>
       </c>
-      <c r="L181" t="s">
-        <v>40</v>
-      </c>
       <c r="M181" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N181" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O181" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P181" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q181">
         <v>92</v>
       </c>
     </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>18</v>
       </c>
@@ -15606,7 +15607,7 @@
         <v>-1</v>
       </c>
       <c r="E182" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F182">
         <v>32</v>
@@ -15624,13 +15625,13 @@
         <v>24</v>
       </c>
       <c r="K182" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L182" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M182" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N182" t="s">
         <v>28</v>
@@ -15645,7 +15646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>18</v>
       </c>
@@ -15659,7 +15660,7 @@
         <v>-1</v>
       </c>
       <c r="E183" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F183">
         <v>32</v>
@@ -15677,28 +15678,28 @@
         <v>24</v>
       </c>
       <c r="K183" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L183" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M183" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N183" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O183">
         <v>0.69499999999999995</v>
       </c>
       <c r="P183" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q183">
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>18</v>
       </c>
@@ -15712,7 +15713,7 @@
         <v>-1</v>
       </c>
       <c r="E184" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F184">
         <v>32</v>
@@ -15730,13 +15731,13 @@
         <v>24</v>
       </c>
       <c r="K184" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L184" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M184" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N184" t="s">
         <v>28</v>
@@ -15745,13 +15746,13 @@
         <v>1.0629999999999999</v>
       </c>
       <c r="P184" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q184">
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>18</v>
       </c>
@@ -15765,7 +15766,7 @@
         <v>-1</v>
       </c>
       <c r="E185" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F185">
         <v>32</v>
@@ -15783,13 +15784,13 @@
         <v>24</v>
       </c>
       <c r="K185" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L185" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M185" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N185" t="s">
         <v>28</v>
@@ -15798,13 +15799,13 @@
         <v>1.042</v>
       </c>
       <c r="P185" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q185">
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>18</v>
       </c>
@@ -15818,7 +15819,7 @@
         <v>-1</v>
       </c>
       <c r="E186" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F186">
         <v>32</v>
@@ -15836,13 +15837,13 @@
         <v>24</v>
       </c>
       <c r="K186" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L186" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M186" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N186" t="s">
         <v>28</v>
@@ -15857,7 +15858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>18</v>
       </c>
@@ -15871,7 +15872,7 @@
         <v>-1</v>
       </c>
       <c r="E187" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F187">
         <v>32</v>
@@ -15889,13 +15890,13 @@
         <v>24</v>
       </c>
       <c r="K187" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L187" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M187" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N187" t="s">
         <v>28</v>
@@ -15904,16 +15905,16 @@
         <v>1.135</v>
       </c>
       <c r="P187" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q187">
         <v>1</v>
       </c>
       <c r="R187" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="188" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>18</v>
       </c>
@@ -15927,7 +15928,7 @@
         <v>-1</v>
       </c>
       <c r="E188" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F188">
         <v>32</v>
@@ -15945,28 +15946,28 @@
         <v>24</v>
       </c>
       <c r="K188" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L188" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M188" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L188" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M188" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="N188" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O188">
         <v>0.49299999999999999</v>
       </c>
       <c r="P188" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q188">
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>18</v>
       </c>
@@ -15980,7 +15981,7 @@
         <v>-1</v>
       </c>
       <c r="E189" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F189">
         <v>32</v>
@@ -15998,28 +15999,28 @@
         <v>24</v>
       </c>
       <c r="K189" t="s">
+        <v>48</v>
+      </c>
+      <c r="L189" t="s">
+        <v>49</v>
+      </c>
+      <c r="M189" t="s">
         <v>50</v>
       </c>
-      <c r="L189" t="s">
-        <v>51</v>
-      </c>
-      <c r="M189" t="s">
-        <v>52</v>
-      </c>
       <c r="N189" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O189">
         <v>0.64100000000000001</v>
       </c>
       <c r="P189" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q189">
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>18</v>
       </c>
@@ -16033,7 +16034,7 @@
         <v>-1</v>
       </c>
       <c r="E190" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F190">
         <v>32</v>
@@ -16051,28 +16052,28 @@
         <v>24</v>
       </c>
       <c r="K190" t="s">
+        <v>48</v>
+      </c>
+      <c r="L190" t="s">
+        <v>49</v>
+      </c>
+      <c r="M190" t="s">
         <v>50</v>
       </c>
-      <c r="L190" t="s">
-        <v>51</v>
-      </c>
-      <c r="M190" t="s">
-        <v>52</v>
-      </c>
       <c r="N190" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O190">
         <v>0.55000000000000004</v>
       </c>
       <c r="P190" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q190">
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>18</v>
       </c>
@@ -16086,7 +16087,7 @@
         <v>-1</v>
       </c>
       <c r="E191" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F191">
         <v>32</v>
@@ -16104,13 +16105,13 @@
         <v>24</v>
       </c>
       <c r="K191" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L191" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M191" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N191" t="s">
         <v>28</v>
@@ -16119,13 +16120,13 @@
         <v>1.4370000000000001</v>
       </c>
       <c r="P191" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q191">
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>18</v>
       </c>
@@ -16139,7 +16140,7 @@
         <v>-1</v>
       </c>
       <c r="E192" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F192">
         <v>32</v>
@@ -16157,28 +16158,28 @@
         <v>24</v>
       </c>
       <c r="K192" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L192" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M192" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L192" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M192" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="N192" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O192">
         <v>0.626</v>
       </c>
       <c r="P192" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q192">
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>18</v>
       </c>
@@ -16192,7 +16193,7 @@
         <v>-1</v>
       </c>
       <c r="E193" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F193">
         <v>32</v>
@@ -16210,28 +16211,28 @@
         <v>24</v>
       </c>
       <c r="K193" t="s">
+        <v>48</v>
+      </c>
+      <c r="L193" t="s">
+        <v>49</v>
+      </c>
+      <c r="M193" t="s">
         <v>50</v>
       </c>
-      <c r="L193" t="s">
-        <v>51</v>
-      </c>
-      <c r="M193" t="s">
-        <v>52</v>
-      </c>
       <c r="N193" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O193">
         <v>0.64100000000000001</v>
       </c>
       <c r="P193" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q193">
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>18</v>
       </c>
@@ -16245,7 +16246,7 @@
         <v>-1</v>
       </c>
       <c r="E194" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F194">
         <v>32</v>
@@ -16263,28 +16264,28 @@
         <v>24</v>
       </c>
       <c r="K194" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L194" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M194" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L194" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M194" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="N194" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O194">
         <v>0.54400000000000004</v>
       </c>
       <c r="P194" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q194">
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>18</v>
       </c>
@@ -16298,7 +16299,7 @@
         <v>-1</v>
       </c>
       <c r="E195" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F195">
         <v>32</v>
@@ -16316,28 +16317,28 @@
         <v>24</v>
       </c>
       <c r="K195" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L195" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M195" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L195" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M195" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="N195" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O195">
         <v>0.61599999999999999</v>
       </c>
       <c r="P195" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q195">
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>18</v>
       </c>
@@ -16351,7 +16352,7 @@
         <v>-1</v>
       </c>
       <c r="E196" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F196">
         <v>32</v>
@@ -16369,13 +16370,13 @@
         <v>24</v>
       </c>
       <c r="K196" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L196" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M196" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N196" t="s">
         <v>28</v>
@@ -16384,13 +16385,13 @@
         <v>1.419</v>
       </c>
       <c r="P196" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q196">
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>18</v>
       </c>
@@ -16404,7 +16405,7 @@
         <v>-1</v>
       </c>
       <c r="E197" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F197">
         <v>32</v>
@@ -16422,28 +16423,28 @@
         <v>24</v>
       </c>
       <c r="K197" t="s">
+        <v>48</v>
+      </c>
+      <c r="L197" t="s">
+        <v>49</v>
+      </c>
+      <c r="M197" t="s">
         <v>50</v>
       </c>
-      <c r="L197" t="s">
-        <v>51</v>
-      </c>
-      <c r="M197" t="s">
-        <v>52</v>
-      </c>
       <c r="N197" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O197">
         <v>0.44400000000000001</v>
       </c>
       <c r="P197" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q197">
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>18</v>
       </c>
@@ -16457,7 +16458,7 @@
         <v>-1</v>
       </c>
       <c r="E198" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F198">
         <v>32</v>
@@ -16475,13 +16476,13 @@
         <v>24</v>
       </c>
       <c r="K198" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L198" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M198" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N198" t="s">
         <v>28</v>
@@ -16496,7 +16497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>18</v>
       </c>
@@ -16510,7 +16511,7 @@
         <v>-1</v>
       </c>
       <c r="E199" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F199">
         <v>32</v>
@@ -16528,28 +16529,28 @@
         <v>24</v>
       </c>
       <c r="K199" t="s">
+        <v>48</v>
+      </c>
+      <c r="L199" t="s">
+        <v>49</v>
+      </c>
+      <c r="M199" t="s">
         <v>50</v>
       </c>
-      <c r="L199" t="s">
-        <v>51</v>
-      </c>
-      <c r="M199" t="s">
-        <v>52</v>
-      </c>
       <c r="N199" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O199">
         <v>1.3140000000000001</v>
       </c>
       <c r="P199" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q199">
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>18</v>
       </c>
@@ -16563,7 +16564,7 @@
         <v>-1</v>
       </c>
       <c r="E200" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F200">
         <v>32</v>
@@ -16581,28 +16582,28 @@
         <v>24</v>
       </c>
       <c r="K200" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L200" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M200" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L200" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M200" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="N200" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O200">
         <v>0.70299999999999996</v>
       </c>
       <c r="P200" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q200">
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>18</v>
       </c>
@@ -16616,7 +16617,7 @@
         <v>-1</v>
       </c>
       <c r="E201" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F201">
         <v>32</v>
@@ -16634,28 +16635,28 @@
         <v>24</v>
       </c>
       <c r="K201" t="s">
+        <v>48</v>
+      </c>
+      <c r="L201" t="s">
+        <v>49</v>
+      </c>
+      <c r="M201" t="s">
         <v>50</v>
       </c>
-      <c r="L201" t="s">
-        <v>51</v>
-      </c>
-      <c r="M201" t="s">
-        <v>52</v>
-      </c>
       <c r="N201" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O201">
         <v>0.93600000000000005</v>
       </c>
       <c r="P201" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q201">
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>18</v>
       </c>
@@ -16669,7 +16670,7 @@
         <v>-1</v>
       </c>
       <c r="E202" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F202">
         <v>32</v>
@@ -16687,13 +16688,13 @@
         <v>24</v>
       </c>
       <c r="K202" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L202" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M202" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N202" t="s">
         <v>28</v>
@@ -16708,7 +16709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>18</v>
       </c>
@@ -16722,7 +16723,7 @@
         <v>-1</v>
       </c>
       <c r="E203" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F203">
         <v>32</v>
@@ -16740,13 +16741,13 @@
         <v>24</v>
       </c>
       <c r="K203" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L203" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M203" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N203" t="s">
         <v>28</v>
@@ -16761,7 +16762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>18</v>
       </c>
@@ -16775,7 +16776,7 @@
         <v>-1</v>
       </c>
       <c r="E204" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F204">
         <v>32</v>
@@ -16793,13 +16794,13 @@
         <v>24</v>
       </c>
       <c r="K204" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L204" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M204" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N204" t="s">
         <v>28</v>
@@ -16814,7 +16815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>18</v>
       </c>
@@ -16828,7 +16829,7 @@
         <v>-1</v>
       </c>
       <c r="E205" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F205">
         <v>32</v>
@@ -16846,13 +16847,13 @@
         <v>24</v>
       </c>
       <c r="K205" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L205" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M205" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N205" t="s">
         <v>28</v>
@@ -16867,7 +16868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>18</v>
       </c>
@@ -16881,7 +16882,7 @@
         <v>-1</v>
       </c>
       <c r="E206" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F206">
         <v>32</v>
@@ -16899,28 +16900,28 @@
         <v>24</v>
       </c>
       <c r="K206" t="s">
+        <v>48</v>
+      </c>
+      <c r="L206" t="s">
+        <v>49</v>
+      </c>
+      <c r="M206" t="s">
         <v>50</v>
       </c>
-      <c r="L206" t="s">
-        <v>51</v>
-      </c>
-      <c r="M206" t="s">
-        <v>52</v>
-      </c>
       <c r="N206" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O206">
         <v>0.75700000000000001</v>
       </c>
       <c r="P206" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q206">
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>18</v>
       </c>
@@ -16934,7 +16935,7 @@
         <v>-1</v>
       </c>
       <c r="E207" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F207">
         <v>32</v>
@@ -16952,19 +16953,19 @@
         <v>24</v>
       </c>
       <c r="K207" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L207" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M207" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N207" t="s">
         <v>28</v>
       </c>
       <c r="O207" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P207" t="s">
         <v>29</v>
@@ -16973,7 +16974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>18</v>
       </c>
@@ -16987,7 +16988,7 @@
         <v>-1</v>
       </c>
       <c r="E208" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F208">
         <v>32</v>
@@ -17005,28 +17006,28 @@
         <v>24</v>
       </c>
       <c r="K208" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L208" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M208" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N208" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O208">
         <v>1.39</v>
       </c>
       <c r="P208" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q208">
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>18</v>
       </c>
@@ -17040,7 +17041,7 @@
         <v>-1</v>
       </c>
       <c r="E209" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F209">
         <v>32</v>
@@ -17058,28 +17059,28 @@
         <v>24</v>
       </c>
       <c r="K209" t="s">
+        <v>48</v>
+      </c>
+      <c r="L209" t="s">
+        <v>49</v>
+      </c>
+      <c r="M209" t="s">
         <v>50</v>
       </c>
-      <c r="L209" t="s">
-        <v>51</v>
-      </c>
-      <c r="M209" t="s">
-        <v>52</v>
-      </c>
       <c r="N209" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O209">
         <v>0.48</v>
       </c>
       <c r="P209" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q209">
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>18</v>
       </c>
@@ -17093,7 +17094,7 @@
         <v>-1</v>
       </c>
       <c r="E210" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F210">
         <v>32</v>
@@ -17111,28 +17112,28 @@
         <v>24</v>
       </c>
       <c r="K210" t="s">
+        <v>48</v>
+      </c>
+      <c r="L210" t="s">
+        <v>49</v>
+      </c>
+      <c r="M210" t="s">
         <v>50</v>
       </c>
-      <c r="L210" t="s">
-        <v>51</v>
-      </c>
-      <c r="M210" t="s">
-        <v>52</v>
-      </c>
       <c r="N210" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O210">
         <v>0.57899999999999996</v>
       </c>
       <c r="P210" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q210">
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>18</v>
       </c>
@@ -17146,7 +17147,7 @@
         <v>-1</v>
       </c>
       <c r="E211" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F211">
         <v>32</v>
@@ -17164,28 +17165,28 @@
         <v>24</v>
       </c>
       <c r="K211" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L211" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M211" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N211" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O211">
         <v>0.999</v>
       </c>
       <c r="P211" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q211">
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>18</v>
       </c>
@@ -17199,7 +17200,7 @@
         <v>-1</v>
       </c>
       <c r="E212" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F212">
         <v>32</v>
@@ -17217,28 +17218,28 @@
         <v>24</v>
       </c>
       <c r="K212" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L212" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M212" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L212" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M212" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="N212" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O212">
         <v>0.55000000000000004</v>
       </c>
       <c r="P212" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q212">
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>18</v>
       </c>
@@ -17252,7 +17253,7 @@
         <v>-1</v>
       </c>
       <c r="E213" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F213">
         <v>32</v>
@@ -17270,28 +17271,28 @@
         <v>24</v>
       </c>
       <c r="K213" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L213" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M213" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L213" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M213" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="N213" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O213" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P213" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q213">
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>18</v>
       </c>
@@ -17305,7 +17306,7 @@
         <v>-1</v>
       </c>
       <c r="E214" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F214">
         <v>32</v>
@@ -17323,19 +17324,19 @@
         <v>24</v>
       </c>
       <c r="K214" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L214" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M214" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N214" t="s">
         <v>28</v>
       </c>
       <c r="O214" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P214" t="s">
         <v>29</v>
@@ -17344,7 +17345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>18</v>
       </c>
@@ -17358,7 +17359,7 @@
         <v>-1</v>
       </c>
       <c r="E215" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F215">
         <v>32</v>
@@ -17376,28 +17377,28 @@
         <v>24</v>
       </c>
       <c r="K215" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L215" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M215" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N215" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O215">
         <v>0.75</v>
       </c>
       <c r="P215" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q215">
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>18</v>
       </c>
@@ -17411,7 +17412,7 @@
         <v>-1</v>
       </c>
       <c r="E216" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F216">
         <v>32</v>
@@ -17429,28 +17430,28 @@
         <v>24</v>
       </c>
       <c r="K216" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L216" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M216" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N216" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O216">
         <v>0.78200000000000003</v>
       </c>
       <c r="P216" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q216">
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>18</v>
       </c>
@@ -17464,7 +17465,7 @@
         <v>-1</v>
       </c>
       <c r="E217" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F217">
         <v>32</v>
@@ -17482,28 +17483,28 @@
         <v>24</v>
       </c>
       <c r="K217" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L217" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M217" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N217" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O217">
         <v>0.95499999999999996</v>
       </c>
       <c r="P217" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q217">
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>18</v>
       </c>
@@ -17517,7 +17518,7 @@
         <v>-1</v>
       </c>
       <c r="E218" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F218">
         <v>32</v>
@@ -17535,28 +17536,28 @@
         <v>24</v>
       </c>
       <c r="K218" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L218" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M218" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N218" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O218" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P218" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q218">
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>18</v>
       </c>
@@ -17570,7 +17571,7 @@
         <v>-1</v>
       </c>
       <c r="E219" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F219">
         <v>32</v>
@@ -17588,28 +17589,28 @@
         <v>24</v>
       </c>
       <c r="K219" t="s">
+        <v>48</v>
+      </c>
+      <c r="L219" t="s">
+        <v>49</v>
+      </c>
+      <c r="M219" t="s">
         <v>50</v>
       </c>
-      <c r="L219" t="s">
-        <v>51</v>
-      </c>
-      <c r="M219" t="s">
-        <v>52</v>
-      </c>
       <c r="N219" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O219">
         <v>0.52300000000000002</v>
       </c>
       <c r="P219" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q219">
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>18</v>
       </c>
@@ -17623,7 +17624,7 @@
         <v>-1</v>
       </c>
       <c r="E220" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F220">
         <v>32</v>
@@ -17641,28 +17642,28 @@
         <v>24</v>
       </c>
       <c r="K220" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L220" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M220" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N220" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O220" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P220" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q220">
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>18</v>
       </c>
@@ -17676,7 +17677,7 @@
         <v>-1</v>
       </c>
       <c r="E221" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F221">
         <v>32</v>
@@ -17694,28 +17695,28 @@
         <v>24</v>
       </c>
       <c r="K221" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L221" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M221" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N221" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O221" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P221" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q221">
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>18</v>
       </c>
@@ -17729,7 +17730,7 @@
         <v>-1</v>
       </c>
       <c r="E222" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F222">
         <v>32</v>
@@ -17747,28 +17748,28 @@
         <v>24</v>
       </c>
       <c r="K222" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L222" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M222" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N222" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O222" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P222" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q222">
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>18</v>
       </c>
@@ -17782,7 +17783,7 @@
         <v>-1</v>
       </c>
       <c r="E223" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F223">
         <v>32</v>
@@ -17800,28 +17801,28 @@
         <v>24</v>
       </c>
       <c r="K223" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L223" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M223" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N223" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O223" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P223" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q223">
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>18</v>
       </c>
@@ -17835,7 +17836,7 @@
         <v>-1</v>
       </c>
       <c r="E224" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F224">
         <v>32</v>
@@ -17853,19 +17854,19 @@
         <v>24</v>
       </c>
       <c r="K224" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L224" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M224" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N224" t="s">
         <v>28</v>
       </c>
       <c r="O224" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P224" t="s">
         <v>29</v>
@@ -17874,7 +17875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>18</v>
       </c>
@@ -17888,7 +17889,7 @@
         <v>-1</v>
       </c>
       <c r="E225" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F225">
         <v>32</v>
@@ -17906,19 +17907,19 @@
         <v>24</v>
       </c>
       <c r="K225" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L225" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M225" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N225" t="s">
         <v>28</v>
       </c>
       <c r="O225" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P225" t="s">
         <v>29</v>
@@ -17927,7 +17928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>18</v>
       </c>
@@ -17941,7 +17942,7 @@
         <v>-1</v>
       </c>
       <c r="E226" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F226">
         <v>32</v>
@@ -17959,28 +17960,28 @@
         <v>24</v>
       </c>
       <c r="K226" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L226" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M226" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N226" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O226" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P226" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q226">
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>18</v>
       </c>
@@ -17994,7 +17995,7 @@
         <v>-1</v>
       </c>
       <c r="E227" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F227">
         <v>32</v>
@@ -18012,28 +18013,28 @@
         <v>24</v>
       </c>
       <c r="K227" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L227" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M227" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N227" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O227" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P227" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q227">
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>18</v>
       </c>
@@ -18047,7 +18048,7 @@
         <v>-1</v>
       </c>
       <c r="E228" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F228">
         <v>32</v>
@@ -18065,28 +18066,28 @@
         <v>24</v>
       </c>
       <c r="K228" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L228" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M228" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N228" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O228" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P228" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q228">
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>18</v>
       </c>
@@ -18100,7 +18101,7 @@
         <v>-1</v>
       </c>
       <c r="E229" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F229">
         <v>32</v>
@@ -18118,28 +18119,28 @@
         <v>24</v>
       </c>
       <c r="K229" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L229" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M229" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="N229" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O229" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P229" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q229">
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>18</v>
       </c>
@@ -18153,7 +18154,7 @@
         <v>-1</v>
       </c>
       <c r="E230" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F230">
         <v>32</v>
@@ -18171,19 +18172,19 @@
         <v>24</v>
       </c>
       <c r="K230" t="s">
+        <v>40</v>
+      </c>
+      <c r="L230" t="s">
+        <v>41</v>
+      </c>
+      <c r="M230" t="s">
         <v>42</v>
-      </c>
-      <c r="L230" t="s">
-        <v>43</v>
-      </c>
-      <c r="M230" t="s">
-        <v>44</v>
       </c>
       <c r="N230" t="s">
         <v>28</v>
       </c>
       <c r="O230" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P230" t="s">
         <v>29</v>
@@ -18192,7 +18193,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="231" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>18</v>
       </c>
@@ -18206,7 +18207,7 @@
         <v>-1</v>
       </c>
       <c r="E231" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F231">
         <v>32</v>
@@ -18224,28 +18225,28 @@
         <v>24</v>
       </c>
       <c r="K231" t="s">
+        <v>40</v>
+      </c>
+      <c r="L231" t="s">
+        <v>41</v>
+      </c>
+      <c r="M231" t="s">
         <v>42</v>
-      </c>
-      <c r="L231" t="s">
-        <v>43</v>
-      </c>
-      <c r="M231" t="s">
-        <v>44</v>
       </c>
       <c r="N231" t="s">
         <v>28</v>
       </c>
       <c r="O231" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P231" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q231">
         <v>11</v>
       </c>
     </row>
-    <row r="232" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>18</v>
       </c>
@@ -18259,7 +18260,7 @@
         <v>-1</v>
       </c>
       <c r="E232" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F232">
         <v>32</v>
@@ -18277,28 +18278,28 @@
         <v>24</v>
       </c>
       <c r="K232" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L232" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M232" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L232" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M232" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="N232" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O232" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P232" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q232">
         <v>5</v>
       </c>
     </row>
-    <row r="233" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>18</v>
       </c>
@@ -18312,7 +18313,7 @@
         <v>-1</v>
       </c>
       <c r="E233" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F233">
         <v>1</v>
@@ -18330,28 +18331,28 @@
         <v>24</v>
       </c>
       <c r="K233" t="s">
+        <v>63</v>
+      </c>
+      <c r="L233" t="s">
+        <v>64</v>
+      </c>
+      <c r="M233" t="s">
         <v>65</v>
       </c>
-      <c r="L233" t="s">
-        <v>66</v>
-      </c>
-      <c r="M233" t="s">
-        <v>67</v>
-      </c>
       <c r="N233" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="O233">
         <v>5.0350000000000001</v>
       </c>
       <c r="P233" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q233">
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>18</v>
       </c>
@@ -18365,7 +18366,7 @@
         <v>-1</v>
       </c>
       <c r="E234" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F234">
         <v>1</v>
@@ -18383,28 +18384,28 @@
         <v>24</v>
       </c>
       <c r="K234" t="s">
+        <v>63</v>
+      </c>
+      <c r="L234" t="s">
+        <v>64</v>
+      </c>
+      <c r="M234" t="s">
         <v>65</v>
       </c>
-      <c r="L234" t="s">
-        <v>66</v>
-      </c>
-      <c r="M234" t="s">
-        <v>67</v>
-      </c>
       <c r="N234" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="O234">
         <v>3.3130000000000002</v>
       </c>
       <c r="P234" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q234">
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>18</v>
       </c>
@@ -18418,7 +18419,7 @@
         <v>-1</v>
       </c>
       <c r="E235" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F235">
         <v>1</v>
@@ -18436,28 +18437,28 @@
         <v>24</v>
       </c>
       <c r="K235" t="s">
+        <v>63</v>
+      </c>
+      <c r="L235" t="s">
+        <v>64</v>
+      </c>
+      <c r="M235" t="s">
         <v>65</v>
       </c>
-      <c r="L235" t="s">
-        <v>66</v>
-      </c>
-      <c r="M235" t="s">
-        <v>67</v>
-      </c>
       <c r="N235" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="O235">
         <v>4.0979999999999999</v>
       </c>
       <c r="P235" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q235">
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>18</v>
       </c>
@@ -18471,7 +18472,7 @@
         <v>-1</v>
       </c>
       <c r="E236" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F236">
         <v>1</v>
@@ -18489,28 +18490,28 @@
         <v>24</v>
       </c>
       <c r="K236" t="s">
+        <v>63</v>
+      </c>
+      <c r="L236" t="s">
+        <v>64</v>
+      </c>
+      <c r="M236" t="s">
         <v>65</v>
       </c>
-      <c r="L236" t="s">
-        <v>66</v>
-      </c>
-      <c r="M236" t="s">
-        <v>67</v>
-      </c>
       <c r="N236" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="O236">
         <v>3.9710000000000001</v>
       </c>
       <c r="P236" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q236">
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>18</v>
       </c>
@@ -18524,7 +18525,7 @@
         <v>-1</v>
       </c>
       <c r="E237" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F237">
         <v>1</v>
@@ -18542,28 +18543,28 @@
         <v>24</v>
       </c>
       <c r="K237" t="s">
+        <v>63</v>
+      </c>
+      <c r="L237" t="s">
+        <v>64</v>
+      </c>
+      <c r="M237" t="s">
         <v>65</v>
       </c>
-      <c r="L237" t="s">
-        <v>66</v>
-      </c>
-      <c r="M237" t="s">
-        <v>67</v>
-      </c>
       <c r="N237" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="O237">
         <v>13.957000000000001</v>
       </c>
       <c r="P237" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q237">
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>18</v>
       </c>
@@ -18577,7 +18578,7 @@
         <v>-1</v>
       </c>
       <c r="E238" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F238">
         <v>1</v>
@@ -18595,28 +18596,28 @@
         <v>24</v>
       </c>
       <c r="K238" t="s">
+        <v>63</v>
+      </c>
+      <c r="L238" t="s">
+        <v>64</v>
+      </c>
+      <c r="M238" t="s">
         <v>65</v>
       </c>
-      <c r="L238" t="s">
-        <v>66</v>
-      </c>
-      <c r="M238" t="s">
-        <v>67</v>
-      </c>
       <c r="N238" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="O238">
         <v>4.0529999999999999</v>
       </c>
       <c r="P238" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q238">
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="4" t="s">
         <v>18</v>
       </c>
@@ -18630,7 +18631,7 @@
         <v>-1</v>
       </c>
       <c r="E239" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F239" s="4">
         <v>64</v>
@@ -18639,7 +18640,7 @@
         <v>22</v>
       </c>
       <c r="H239" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I239" s="4" t="s">
         <v>23</v>
@@ -18648,28 +18649,28 @@
         <v>24</v>
       </c>
       <c r="K239" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="L239" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="M239" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="L239" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="M239" s="4" t="s">
-        <v>52</v>
-      </c>
       <c r="N239" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O239" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P239" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q239" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="4" t="s">
         <v>18</v>
       </c>
@@ -18683,46 +18684,46 @@
         <v>-1</v>
       </c>
       <c r="E240" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F240" s="4">
+        <v>64</v>
+      </c>
+      <c r="G240" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H240" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I240" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J240" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K240" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F240" s="4">
-        <v>64</v>
-      </c>
-      <c r="G240" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H240" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I240" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="J240" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="K240" s="4" t="s">
-        <v>61</v>
-      </c>
       <c r="L240" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M240" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N240" s="4" t="s">
         <v>28</v>
       </c>
       <c r="O240" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P240" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q240" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="4" t="s">
         <v>18</v>
       </c>
@@ -18745,7 +18746,7 @@
         <v>22</v>
       </c>
       <c r="H241" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I241" s="4" t="s">
         <v>23</v>
@@ -18754,28 +18755,35 @@
         <v>24</v>
       </c>
       <c r="K241" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L241" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M241" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N241" s="4" t="s">
         <v>28</v>
       </c>
       <c r="O241" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P241" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q241" s="4">
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:R241" xr:uid="{E093411B-5FC0-41F2-9B42-F2A8D6145550}">
+    <filterColumn colId="12">
+      <filters>
+        <filter val="CYCIM"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId2"/>
